--- a/Base Cana BI 2.xlsx
+++ b/Base Cana BI 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iago\Desktop\Projeto AFB Itapira - Automação de dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE5E66D-CC03-42F9-886F-35A7AB292064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6FD7B1-FF4B-42AE-B369-33857F8886DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{966E7219-A113-4A27-A97B-015265CE31ED}"/>
   </bookViews>
@@ -750,7 +750,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05B88DED-2186-4B06-A0DC-FB0B7B55563E}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:N788"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -807,7 +806,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>2025</v>
       </c>
@@ -843,7 +842,7 @@
         <v>1366.18</v>
       </c>
     </row>
-    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2025</v>
       </c>
@@ -879,7 +878,7 @@
         <v>2371.6800000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2025</v>
       </c>
@@ -915,7 +914,7 @@
         <v>1570.92</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>2025</v>
       </c>
@@ -951,7 +950,7 @@
         <v>3035.31</v>
       </c>
     </row>
-    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2025</v>
       </c>
@@ -987,7 +986,7 @@
         <v>580.58000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2025</v>
       </c>
@@ -1023,7 +1022,7 @@
         <v>510.12</v>
       </c>
     </row>
-    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>2025</v>
       </c>
@@ -1059,7 +1058,7 @@
         <v>382.98</v>
       </c>
     </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>2025</v>
       </c>
@@ -1095,7 +1094,7 @@
         <v>563.16</v>
       </c>
     </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>2025</v>
       </c>
@@ -1131,7 +1130,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>2025</v>
       </c>
@@ -1167,7 +1166,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>2025</v>
       </c>
@@ -1203,7 +1202,7 @@
         <v>770.40000000000009</v>
       </c>
     </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>2025</v>
       </c>
@@ -1239,7 +1238,7 @@
         <v>361.25</v>
       </c>
     </row>
-    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>2025</v>
       </c>
@@ -1275,7 +1274,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>2025</v>
       </c>
@@ -1317,7 +1316,7 @@
         <v>396.24</v>
       </c>
     </row>
-    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>2025</v>
       </c>
@@ -1353,7 +1352,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>2025</v>
       </c>
@@ -1389,7 +1388,7 @@
         <v>2153.84</v>
       </c>
     </row>
-    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>2025</v>
       </c>
@@ -1429,7 +1428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>2025</v>
       </c>
@@ -1465,7 +1464,7 @@
         <v>1090.8</v>
       </c>
     </row>
-    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>2025</v>
       </c>
@@ -1501,7 +1500,7 @@
         <v>1028.7</v>
       </c>
     </row>
-    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>2025</v>
       </c>
@@ -1537,7 +1536,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>2025</v>
       </c>
@@ -1573,7 +1572,7 @@
         <v>2660</v>
       </c>
     </row>
-    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>2025</v>
       </c>
@@ -1609,7 +1608,7 @@
         <v>3203.5199999999995</v>
       </c>
     </row>
-    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>2025</v>
       </c>
@@ -1681,7 +1680,7 @@
         <v>3012.24</v>
       </c>
     </row>
-    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>2025</v>
       </c>
@@ -1717,7 +1716,7 @@
         <v>835.5</v>
       </c>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>2025</v>
       </c>
@@ -1753,7 +1752,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>2025</v>
       </c>
@@ -1789,7 +1788,7 @@
         <v>669.56000000000006</v>
       </c>
     </row>
-    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>2025</v>
       </c>
@@ -1828,7 +1827,7 @@
         <v>708.76</v>
       </c>
     </row>
-    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>2025</v>
       </c>
@@ -1864,7 +1863,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>2025</v>
       </c>
@@ -1900,7 +1899,7 @@
         <v>1622.5</v>
       </c>
     </row>
-    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>2025</v>
       </c>
@@ -1936,7 +1935,7 @@
         <v>2413.4</v>
       </c>
     </row>
-    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>2025</v>
       </c>
@@ -1972,7 +1971,7 @@
         <v>5162.1099999999997</v>
       </c>
     </row>
-    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>2025</v>
       </c>
@@ -2008,7 +2007,7 @@
         <v>74.734000000000009</v>
       </c>
     </row>
-    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>2025</v>
       </c>
@@ -2044,7 +2043,7 @@
         <v>642.39</v>
       </c>
     </row>
-    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>2025</v>
       </c>
@@ -2080,7 +2079,7 @@
         <v>1773.77</v>
       </c>
     </row>
-    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>2025</v>
       </c>
@@ -2116,7 +2115,7 @@
         <v>759.17</v>
       </c>
     </row>
-    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>2025</v>
       </c>
@@ -2152,7 +2151,7 @@
         <v>805.45</v>
       </c>
     </row>
-    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>2025</v>
       </c>
@@ -2188,7 +2187,7 @@
         <v>1228.2</v>
       </c>
     </row>
-    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>2025</v>
       </c>
@@ -2224,7 +2223,7 @@
         <v>646.14</v>
       </c>
     </row>
-    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>2025</v>
       </c>
@@ -2260,7 +2259,7 @@
         <v>2104.6</v>
       </c>
     </row>
-    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>2025</v>
       </c>
@@ -2296,7 +2295,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>2025</v>
       </c>
@@ -2332,7 +2331,7 @@
         <v>1405.8999999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>2025</v>
       </c>
@@ -2368,7 +2367,7 @@
         <v>179.82999999999998</v>
       </c>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>2025</v>
       </c>
@@ -2404,7 +2403,7 @@
         <v>146.51000000000002</v>
       </c>
     </row>
-    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>2025</v>
       </c>
@@ -2440,7 +2439,7 @@
         <v>1557.0000000000002</v>
       </c>
     </row>
-    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>2025</v>
       </c>
@@ -2476,7 +2475,7 @@
         <v>4760.4000000000005</v>
       </c>
     </row>
-    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>2025</v>
       </c>
@@ -2512,7 +2511,7 @@
         <v>1970.27</v>
       </c>
     </row>
-    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>2025</v>
       </c>
@@ -2548,7 +2547,7 @@
         <v>3109.66</v>
       </c>
     </row>
-    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>2025</v>
       </c>
@@ -2584,7 +2583,7 @@
         <v>2797.36</v>
       </c>
     </row>
-    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>2025</v>
       </c>
@@ -2624,7 +2623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>2025</v>
       </c>
@@ -2664,7 +2663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>2025</v>
       </c>
@@ -2704,7 +2703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>2025</v>
       </c>
@@ -2740,7 +2739,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>2025</v>
       </c>
@@ -2779,7 +2778,7 @@
         <v>1198.0880000000002</v>
       </c>
     </row>
-    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>2025</v>
       </c>
@@ -2815,7 +2814,7 @@
         <v>1582.2</v>
       </c>
     </row>
-    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>2025</v>
       </c>
@@ -2854,7 +2853,7 @@
         <v>606.83800000000008</v>
       </c>
     </row>
-    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>2025</v>
       </c>
@@ -2894,7 +2893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>2025</v>
       </c>
@@ -2930,7 +2929,7 @@
         <v>3234.2499999999995</v>
       </c>
     </row>
-    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>2025</v>
       </c>
@@ -2966,7 +2965,7 @@
         <v>725.1099999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>2025</v>
       </c>
@@ -3002,7 +3001,7 @@
         <v>943.6</v>
       </c>
     </row>
-    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>2025</v>
       </c>
@@ -3038,7 +3037,7 @@
         <v>4113</v>
       </c>
     </row>
-    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>2015</v>
       </c>
@@ -3074,7 +3073,7 @@
         <v>1371.5267999999999</v>
       </c>
     </row>
-    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>2015</v>
       </c>
@@ -3110,7 +3109,7 @@
         <v>390.39119999999997</v>
       </c>
     </row>
-    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>2015</v>
       </c>
@@ -3146,7 +3145,7 @@
         <v>760.38460000000009</v>
       </c>
     </row>
-    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>2015</v>
       </c>
@@ -3182,7 +3181,7 @@
         <v>921.63679999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>2015</v>
       </c>
@@ -3218,7 +3217,7 @@
         <v>807.32299999999998</v>
       </c>
     </row>
-    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>2015</v>
       </c>
@@ -3254,7 +3253,7 @@
         <v>1669.5090000000002</v>
       </c>
     </row>
-    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>2015</v>
       </c>
@@ -3290,7 +3289,7 @@
         <v>1071.9518</v>
       </c>
     </row>
-    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>2015</v>
       </c>
@@ -3326,7 +3325,7 @@
         <v>925.25249999999994</v>
       </c>
     </row>
-    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>2015</v>
       </c>
@@ -3362,7 +3361,7 @@
         <v>330.8261</v>
       </c>
     </row>
-    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>2015</v>
       </c>
@@ -3398,7 +3397,7 @@
         <v>270.38149999999996</v>
       </c>
     </row>
-    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>2015</v>
       </c>
@@ -3434,7 +3433,7 @@
         <v>664.56260000000009</v>
       </c>
     </row>
-    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>2015</v>
       </c>
@@ -3470,7 +3469,7 @@
         <v>449.85599999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>2015</v>
       </c>
@@ -3506,7 +3505,7 @@
         <v>655.81299999999999</v>
       </c>
     </row>
-    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>2015</v>
       </c>
@@ -3542,7 +3541,7 @@
         <v>670.14640000000009</v>
       </c>
     </row>
-    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>2015</v>
       </c>
@@ -3578,7 +3577,7 @@
         <v>593.9325</v>
       </c>
     </row>
-    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>2015</v>
       </c>
@@ -3614,7 +3613,7 @@
         <v>422.01160000000004</v>
       </c>
     </row>
-    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>2015</v>
       </c>
@@ -3650,7 +3649,7 @@
         <v>512.02679999999998</v>
       </c>
     </row>
-    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>2015</v>
       </c>
@@ -3692,7 +3691,7 @@
         <v>691.41600000000005</v>
       </c>
     </row>
-    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>2015</v>
       </c>
@@ -3728,7 +3727,7 @@
         <v>775.88019999999995</v>
       </c>
     </row>
-    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>2015</v>
       </c>
@@ -3764,7 +3763,7 @@
         <v>684.52800000000002</v>
       </c>
     </row>
-    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>2015</v>
       </c>
@@ -3800,7 +3799,7 @@
         <v>753.24839999999995</v>
       </c>
     </row>
-    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>2015</v>
       </c>
@@ -3836,7 +3835,7 @@
         <v>1392.78</v>
       </c>
     </row>
-    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>2015</v>
       </c>
@@ -3872,7 +3871,7 @@
         <v>955.69600000000003</v>
       </c>
     </row>
-    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>2015</v>
       </c>
@@ -3908,7 +3907,7 @@
         <v>1045.3374000000001</v>
       </c>
     </row>
-    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>2015</v>
       </c>
@@ -3944,7 +3943,7 @@
         <v>713.57500000000005</v>
       </c>
     </row>
-    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>2015</v>
       </c>
@@ -3980,7 +3979,7 @@
         <v>177.4528</v>
       </c>
     </row>
-    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>2015</v>
       </c>
@@ -4052,7 +4051,7 @@
         <v>505.86570000000006</v>
       </c>
     </row>
-    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>2015</v>
       </c>
@@ -4088,7 +4087,7 @@
         <v>1271.7705000000001</v>
       </c>
     </row>
-    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>2015</v>
       </c>
@@ -4124,7 +4123,7 @@
         <v>210.86489999999998</v>
       </c>
     </row>
-    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>2015</v>
       </c>
@@ -4160,7 +4159,7 @@
         <v>417.32</v>
       </c>
     </row>
-    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>2015</v>
       </c>
@@ -4196,7 +4195,7 @@
         <v>583.09899999999993</v>
       </c>
     </row>
-    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>2015</v>
       </c>
@@ -4232,7 +4231,7 @@
         <v>476.11619999999994</v>
       </c>
     </row>
-    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>2015</v>
       </c>
@@ -4268,7 +4267,7 @@
         <v>336.97800000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>2015</v>
       </c>
@@ -4304,7 +4303,7 @@
         <v>286.20059999999995</v>
       </c>
     </row>
-    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>2015</v>
       </c>
@@ -4340,7 +4339,7 @@
         <v>293.12</v>
       </c>
     </row>
-    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>2015</v>
       </c>
@@ -4376,7 +4375,7 @@
         <v>59.167899999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>2015</v>
       </c>
@@ -4412,7 +4411,7 @@
         <v>184.2688</v>
       </c>
     </row>
-    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>2015</v>
       </c>
@@ -4448,7 +4447,7 @@
         <v>169.10169999999999</v>
       </c>
     </row>
-    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>2015</v>
       </c>
@@ -4484,7 +4483,7 @@
         <v>383.22019999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>2015</v>
       </c>
@@ -4520,7 +4519,7 @@
         <v>340.08719999999994</v>
       </c>
     </row>
-    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>2015</v>
       </c>
@@ -4556,7 +4555,7 @@
         <v>379.5446</v>
       </c>
     </row>
-    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>2015</v>
       </c>
@@ -4592,7 +4591,7 @@
         <v>290.93739999999997</v>
       </c>
     </row>
-    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>2015</v>
       </c>
@@ -4628,7 +4627,7 @@
         <v>954.9</v>
       </c>
     </row>
-    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>2015</v>
       </c>
@@ -4664,7 +4663,7 @@
         <v>1231.8362</v>
       </c>
     </row>
-    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>2015</v>
       </c>
@@ -4700,7 +4699,7 @@
         <v>960.92279999999994</v>
       </c>
     </row>
-    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>2015</v>
       </c>
@@ -4736,7 +4735,7 @@
         <v>476.70310000000006</v>
       </c>
     </row>
-    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>2015</v>
       </c>
@@ -4772,7 +4771,7 @@
         <v>135.1694</v>
       </c>
     </row>
-    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>2015</v>
       </c>
@@ -4808,7 +4807,7 @@
         <v>1409.7483</v>
       </c>
     </row>
-    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>2015</v>
       </c>
@@ -4844,7 +4843,7 @@
         <v>2415.3854999999999</v>
       </c>
     </row>
-    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>2015</v>
       </c>
@@ -4880,7 +4879,7 @@
         <v>1631.1839999999997</v>
       </c>
     </row>
-    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>2015</v>
       </c>
@@ -4916,7 +4915,7 @@
         <v>723.60339999999997</v>
       </c>
     </row>
-    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>2015</v>
       </c>
@@ -4952,7 +4951,7 @@
         <v>1847.2080999999998</v>
       </c>
     </row>
-    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>2015</v>
       </c>
@@ -4988,7 +4987,7 @@
         <v>773.57279999999992</v>
       </c>
     </row>
-    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>2015</v>
       </c>
@@ -5024,7 +5023,7 @@
         <v>143.50470000000001</v>
       </c>
     </row>
-    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>2015</v>
       </c>
@@ -5060,7 +5059,7 @@
         <v>891.09979999999996</v>
       </c>
     </row>
-    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>2015</v>
       </c>
@@ -5096,7 +5095,7 @@
         <v>1474.0411000000001</v>
       </c>
     </row>
-    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>2015</v>
       </c>
@@ -5132,7 +5131,7 @@
         <v>78.759</v>
       </c>
     </row>
-    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>2015</v>
       </c>
@@ -5168,7 +5167,7 @@
         <v>355.27190000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>2015</v>
       </c>
@@ -5204,7 +5203,7 @@
         <v>580.46679999999992</v>
       </c>
     </row>
-    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>2015</v>
       </c>
@@ -5240,7 +5239,7 @@
         <v>502.20099999999996</v>
       </c>
     </row>
-    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>2015</v>
       </c>
@@ -5276,7 +5275,7 @@
         <v>725.82159999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>2015</v>
       </c>
@@ -5312,7 +5311,7 @@
         <v>1206.1764000000001</v>
       </c>
     </row>
-    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>2015</v>
       </c>
@@ -5348,7 +5347,7 @@
         <v>1879.4970000000001</v>
       </c>
     </row>
-    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>2015</v>
       </c>
@@ -5384,7 +5383,7 @@
         <v>307.9502</v>
       </c>
     </row>
-    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>2015</v>
       </c>
@@ -5420,7 +5419,7 @@
         <v>420.61599999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>2015</v>
       </c>
@@ -5456,7 +5455,7 @@
         <v>776.51049999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>2015</v>
       </c>
@@ -5492,7 +5491,7 @@
         <v>1096.8047999999999</v>
       </c>
     </row>
-    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>2015</v>
       </c>
@@ -5528,7 +5527,7 @@
         <v>659.02319999999997</v>
       </c>
     </row>
-    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>2015</v>
       </c>
@@ -5564,7 +5563,7 @@
         <v>1910.1158999999998</v>
       </c>
     </row>
-    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>2015</v>
       </c>
@@ -5600,7 +5599,7 @@
         <v>519.80359999999996</v>
       </c>
     </row>
-    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>2015</v>
       </c>
@@ -5636,7 +5635,7 @@
         <v>104.229</v>
       </c>
     </row>
-    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>2015</v>
       </c>
@@ -5672,7 +5671,7 @@
         <v>105.996</v>
       </c>
     </row>
-    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>2015</v>
       </c>
@@ -5708,7 +5707,7 @@
         <v>80.339600000000004</v>
       </c>
     </row>
-    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>2015</v>
       </c>
@@ -5744,7 +5743,7 @@
         <v>122.0856</v>
       </c>
     </row>
-    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>2015</v>
       </c>
@@ -5780,7 +5779,7 @@
         <v>782.38440000000003</v>
       </c>
     </row>
-    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>2015</v>
       </c>
@@ -5816,7 +5815,7 @@
         <v>680.43780000000015</v>
       </c>
     </row>
-    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>2015</v>
       </c>
@@ -5852,7 +5851,7 @@
         <v>664.91279999999995</v>
       </c>
     </row>
-    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>2015</v>
       </c>
@@ -5888,7 +5887,7 @@
         <v>420.96600000000001</v>
       </c>
     </row>
-    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>2015</v>
       </c>
@@ -5924,7 +5923,7 @@
         <v>98.580300000000008</v>
       </c>
     </row>
-    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>2015</v>
       </c>
@@ -5960,7 +5959,7 @@
         <v>319.73759999999999</v>
       </c>
     </row>
-    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>2015</v>
       </c>
@@ -5996,7 +5995,7 @@
         <v>353.85899999999998</v>
       </c>
     </row>
-    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>2015</v>
       </c>
@@ -6032,7 +6031,7 @@
         <v>409.01250000000005</v>
       </c>
     </row>
-    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>2016</v>
       </c>
@@ -6068,7 +6067,7 @@
         <v>1358.4738</v>
       </c>
     </row>
-    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>2016</v>
       </c>
@@ -6104,7 +6103,7 @@
         <v>226.25319999999999</v>
       </c>
     </row>
-    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>2016</v>
       </c>
@@ -6140,7 +6139,7 @@
         <v>792.33619999999996</v>
       </c>
     </row>
-    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>2016</v>
       </c>
@@ -6176,7 +6175,7 @@
         <v>792.4144</v>
       </c>
     </row>
-    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>2016</v>
       </c>
@@ -6212,7 +6211,7 @@
         <v>1132.0484999999999</v>
       </c>
     </row>
-    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>2016</v>
       </c>
@@ -6248,7 +6247,7 @@
         <v>1358.4090000000001</v>
       </c>
     </row>
-    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>2016</v>
       </c>
@@ -6284,7 +6283,7 @@
         <v>679.13900000000001</v>
       </c>
     </row>
-    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>2016</v>
       </c>
@@ -6320,7 +6319,7 @@
         <v>679.1721</v>
       </c>
     </row>
-    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>2016</v>
       </c>
@@ -6356,7 +6355,7 @@
         <v>1132.0613000000001</v>
       </c>
     </row>
-    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>2016</v>
       </c>
@@ -6392,7 +6391,7 @@
         <v>415.6352</v>
       </c>
     </row>
-    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>2016</v>
       </c>
@@ -6428,7 +6427,7 @@
         <v>310.96180000000004</v>
       </c>
     </row>
-    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>2016</v>
       </c>
@@ -6464,7 +6463,7 @@
         <v>430.77600000000001</v>
       </c>
     </row>
-    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>2016</v>
       </c>
@@ -6500,7 +6499,7 @@
         <v>440.68900000000002</v>
       </c>
     </row>
-    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>2016</v>
       </c>
@@ -6536,7 +6535,7 @@
         <v>841.96560000000011</v>
       </c>
     </row>
-    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>2016</v>
       </c>
@@ -6572,7 +6571,7 @@
         <v>517.76549999999997</v>
       </c>
     </row>
-    <row r="161" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>2016</v>
       </c>
@@ -6608,7 +6607,7 @@
         <v>186.84200000000001</v>
       </c>
     </row>
-    <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>2016</v>
       </c>
@@ -6644,7 +6643,7 @@
         <v>62.255400000000002</v>
       </c>
     </row>
-    <row r="163" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>2016</v>
       </c>
@@ -6686,7 +6685,7 @@
         <v>308.97900000000004</v>
       </c>
     </row>
-    <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>2016</v>
       </c>
@@ -6722,7 +6721,7 @@
         <v>1245.8126</v>
       </c>
     </row>
-    <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>2016</v>
       </c>
@@ -6758,7 +6757,7 @@
         <v>249.14240000000001</v>
       </c>
     </row>
-    <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>2016</v>
       </c>
@@ -6794,7 +6793,7 @@
         <v>311.60360000000003</v>
       </c>
     </row>
-    <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>2016</v>
       </c>
@@ -6830,7 +6829,7 @@
         <v>394.98840000000001</v>
       </c>
     </row>
-    <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>2016</v>
       </c>
@@ -6866,7 +6865,7 @@
         <v>242.20700000000002</v>
       </c>
     </row>
-    <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>2016</v>
       </c>
@@ -6902,7 +6901,7 @@
         <v>369.57120000000003</v>
       </c>
     </row>
-    <row r="170" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>2016</v>
       </c>
@@ -6938,7 +6937,7 @@
         <v>178.2</v>
       </c>
     </row>
-    <row r="171" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>2016</v>
       </c>
@@ -6974,7 +6973,7 @@
         <v>258.35039999999998</v>
       </c>
     </row>
-    <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>2016</v>
       </c>
@@ -7046,7 +7045,7 @@
         <v>282.14100000000002</v>
       </c>
     </row>
-    <row r="174" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>2016</v>
       </c>
@@ -7082,7 +7081,7 @@
         <v>612.88920000000007</v>
       </c>
     </row>
-    <row r="175" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>2016</v>
       </c>
@@ -7118,7 +7117,7 @@
         <v>375.00479999999999</v>
       </c>
     </row>
-    <row r="176" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>2016</v>
       </c>
@@ -7154,7 +7153,7 @@
         <v>212.48820000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>2016</v>
       </c>
@@ -7190,7 +7189,7 @@
         <v>377.01089999999999</v>
       </c>
     </row>
-    <row r="178" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>2016</v>
       </c>
@@ -7226,7 +7225,7 @@
         <v>306.31039999999996</v>
       </c>
     </row>
-    <row r="179" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>2016</v>
       </c>
@@ -7262,7 +7261,7 @@
         <v>168.24499999999998</v>
       </c>
     </row>
-    <row r="180" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>2016</v>
       </c>
@@ -7298,7 +7297,7 @@
         <v>258.83519999999999</v>
       </c>
     </row>
-    <row r="181" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>2016</v>
       </c>
@@ -7334,7 +7333,7 @@
         <v>276.77019999999999</v>
       </c>
     </row>
-    <row r="182" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>2016</v>
       </c>
@@ -7370,7 +7369,7 @@
         <v>309.2543</v>
       </c>
     </row>
-    <row r="183" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>2016</v>
       </c>
@@ -7406,7 +7405,7 @@
         <v>398.08139999999997</v>
       </c>
     </row>
-    <row r="184" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>2016</v>
       </c>
@@ -7442,7 +7441,7 @@
         <v>266.55600000000004</v>
       </c>
     </row>
-    <row r="185" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>2016</v>
       </c>
@@ -7478,7 +7477,7 @@
         <v>219.626</v>
       </c>
     </row>
-    <row r="186" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>2016</v>
       </c>
@@ -7514,7 +7513,7 @@
         <v>297.44920000000002</v>
       </c>
     </row>
-    <row r="187" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>2016</v>
       </c>
@@ -7550,7 +7549,7 @@
         <v>231.32990000000004</v>
       </c>
     </row>
-    <row r="188" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>2016</v>
       </c>
@@ -7586,7 +7585,7 @@
         <v>505.98900000000003</v>
       </c>
     </row>
-    <row r="189" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>2016</v>
       </c>
@@ -7622,7 +7621,7 @@
         <v>859.25139999999999</v>
       </c>
     </row>
-    <row r="190" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>2016</v>
       </c>
@@ -7658,7 +7657,7 @@
         <v>540.29399999999998</v>
       </c>
     </row>
-    <row r="191" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>2016</v>
       </c>
@@ -7694,7 +7693,7 @@
         <v>342.62179999999995</v>
       </c>
     </row>
-    <row r="192" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>2016</v>
       </c>
@@ -7730,7 +7729,7 @@
         <v>514.97419999999988</v>
       </c>
     </row>
-    <row r="193" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>2016</v>
       </c>
@@ -7766,7 +7765,7 @@
         <v>470.08319999999992</v>
       </c>
     </row>
-    <row r="194" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>2016</v>
       </c>
@@ -7802,7 +7801,7 @@
         <v>502.09209999999996</v>
       </c>
     </row>
-    <row r="195" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>2016</v>
       </c>
@@ -7838,7 +7837,7 @@
         <v>487.99730000000005</v>
       </c>
     </row>
-    <row r="196" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>2016</v>
       </c>
@@ -7874,7 +7873,7 @@
         <v>56.439</v>
       </c>
     </row>
-    <row r="197" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>2016</v>
       </c>
@@ -7910,7 +7909,7 @@
         <v>907.52200000000016</v>
       </c>
     </row>
-    <row r="198" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>2016</v>
       </c>
@@ -7946,7 +7945,7 @@
         <v>797.86200000000008</v>
       </c>
     </row>
-    <row r="199" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>2016</v>
       </c>
@@ -7982,7 +7981,7 @@
         <v>1329.8354999999999</v>
       </c>
     </row>
-    <row r="200" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>2016</v>
       </c>
@@ -8018,7 +8017,7 @@
         <v>797.84579999999994</v>
       </c>
     </row>
-    <row r="201" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>2016</v>
       </c>
@@ -8054,7 +8053,7 @@
         <v>797.84120000000007</v>
       </c>
     </row>
-    <row r="202" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>2016</v>
       </c>
@@ -8090,7 +8089,7 @@
         <v>1329.8927999999999</v>
       </c>
     </row>
-    <row r="203" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>2016</v>
       </c>
@@ -8126,7 +8125,7 @@
         <v>664.86799999999994</v>
       </c>
     </row>
-    <row r="204" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>2016</v>
       </c>
@@ -8162,7 +8161,7 @@
         <v>531.86</v>
       </c>
     </row>
-    <row r="205" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>2016</v>
       </c>
@@ -8198,7 +8197,7 @@
         <v>664.82819999999992</v>
       </c>
     </row>
-    <row r="206" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>2016</v>
       </c>
@@ -8234,7 +8233,7 @@
         <v>797.82730000000004</v>
       </c>
     </row>
-    <row r="207" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>2016</v>
       </c>
@@ -8270,7 +8269,7 @@
         <v>265.82010000000002</v>
       </c>
     </row>
-    <row r="208" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>2016</v>
       </c>
@@ -8306,7 +8305,7 @@
         <v>797.80049999999994</v>
       </c>
     </row>
-    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>2016</v>
       </c>
@@ -8342,7 +8341,7 @@
         <v>267.83639999999997</v>
       </c>
     </row>
-    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>2016</v>
       </c>
@@ -8378,7 +8377,7 @@
         <v>329.50349999999997</v>
       </c>
     </row>
-    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>2016</v>
       </c>
@@ -8414,7 +8413,7 @@
         <v>405.00399999999996</v>
       </c>
     </row>
-    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>2016</v>
       </c>
@@ -8450,7 +8449,7 @@
         <v>432.14929999999998</v>
       </c>
     </row>
-    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>2016</v>
       </c>
@@ -8486,7 +8485,7 @@
         <v>399.72659999999996</v>
       </c>
     </row>
-    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>2016</v>
       </c>
@@ -8522,7 +8521,7 @@
         <v>532.3578</v>
       </c>
     </row>
-    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>2016</v>
       </c>
@@ -8558,7 +8557,7 @@
         <v>551.08440000000007</v>
       </c>
     </row>
-    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>2016</v>
       </c>
@@ -8594,7 +8593,7 @@
         <v>225.84130000000002</v>
       </c>
     </row>
-    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>2016</v>
       </c>
@@ -8630,7 +8629,7 @@
         <v>167.232</v>
       </c>
     </row>
-    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>2016</v>
       </c>
@@ -8666,7 +8665,7 @@
         <v>1545.2411</v>
       </c>
     </row>
-    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>2016</v>
       </c>
@@ -8702,7 +8701,7 @@
         <v>192.77440000000001</v>
       </c>
     </row>
-    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>2016</v>
       </c>
@@ -8738,7 +8737,7 @@
         <v>168.16800000000001</v>
       </c>
     </row>
-    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>2016</v>
       </c>
@@ -8774,7 +8773,7 @@
         <v>504.46500000000003</v>
       </c>
     </row>
-    <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>2017</v>
       </c>
@@ -8810,7 +8809,7 @@
         <v>804.50320000000011</v>
       </c>
     </row>
-    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>2017</v>
       </c>
@@ -8846,7 +8845,7 @@
         <v>765.18400000000008</v>
       </c>
     </row>
-    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>2017</v>
       </c>
@@ -8882,7 +8881,7 @@
         <v>993.4045000000001</v>
       </c>
     </row>
-    <row r="225" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>2017</v>
       </c>
@@ -8918,7 +8917,7 @@
         <v>1397.7539999999999</v>
       </c>
     </row>
-    <row r="226" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>2017</v>
       </c>
@@ -8954,7 +8953,7 @@
         <v>976.24360000000001</v>
       </c>
     </row>
-    <row r="227" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>2017</v>
       </c>
@@ -8990,7 +8989,7 @@
         <v>905.48109999999997</v>
       </c>
     </row>
-    <row r="228" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>2017</v>
       </c>
@@ -9026,7 +9025,7 @@
         <v>983.55649999999991</v>
       </c>
     </row>
-    <row r="229" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>2017</v>
       </c>
@@ -9062,7 +9061,7 @@
         <v>581.07910000000004</v>
       </c>
     </row>
-    <row r="230" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>2017</v>
       </c>
@@ -9098,7 +9097,7 @@
         <v>348.6146</v>
       </c>
     </row>
-    <row r="231" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>2017</v>
       </c>
@@ -9134,7 +9133,7 @@
         <v>576.28800000000001</v>
       </c>
     </row>
-    <row r="232" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>2017</v>
       </c>
@@ -9170,7 +9169,7 @@
         <v>576.32349999999997</v>
       </c>
     </row>
-    <row r="233" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>2017</v>
       </c>
@@ -9206,7 +9205,7 @@
         <v>1008.6328000000001</v>
       </c>
     </row>
-    <row r="234" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>2017</v>
       </c>
@@ -9242,7 +9241,7 @@
         <v>576.26099999999997</v>
       </c>
     </row>
-    <row r="235" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>2017</v>
       </c>
@@ -9284,7 +9283,7 @@
         <v>360.16200000000003</v>
       </c>
     </row>
-    <row r="236" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>2017</v>
       </c>
@@ -9320,7 +9319,7 @@
         <v>432.19600000000003</v>
       </c>
     </row>
-    <row r="237" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>2017</v>
       </c>
@@ -9356,7 +9355,7 @@
         <v>363.286</v>
       </c>
     </row>
-    <row r="238" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>2017</v>
       </c>
@@ -9392,7 +9391,7 @@
         <v>302.70150000000007</v>
       </c>
     </row>
-    <row r="239" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>2017</v>
       </c>
@@ -9428,7 +9427,7 @@
         <v>181.57499999999999</v>
       </c>
     </row>
-    <row r="240" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>2017</v>
       </c>
@@ -9464,7 +9463,7 @@
         <v>363.29359999999997</v>
       </c>
     </row>
-    <row r="241" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>2017</v>
       </c>
@@ -9536,7 +9535,7 @@
         <v>363.2724</v>
       </c>
     </row>
-    <row r="243" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>2017</v>
       </c>
@@ -9572,7 +9571,7 @@
         <v>605.60500000000002</v>
       </c>
     </row>
-    <row r="244" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>2017</v>
       </c>
@@ -9608,7 +9607,7 @@
         <v>181.56709999999998</v>
       </c>
     </row>
-    <row r="245" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>2017</v>
       </c>
@@ -9644,7 +9643,7 @@
         <v>726.75639999999999</v>
       </c>
     </row>
-    <row r="246" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>2017</v>
       </c>
@@ -9680,7 +9679,7 @@
         <v>423.96839999999997</v>
       </c>
     </row>
-    <row r="247" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>2017</v>
       </c>
@@ -9716,7 +9715,7 @@
         <v>242.14109999999999</v>
       </c>
     </row>
-    <row r="248" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>2017</v>
       </c>
@@ -9752,7 +9751,7 @@
         <v>484.43779999999992</v>
       </c>
     </row>
-    <row r="249" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>2017</v>
       </c>
@@ -9788,7 +9787,7 @@
         <v>363.28559999999999</v>
       </c>
     </row>
-    <row r="250" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>2017</v>
       </c>
@@ -9824,7 +9823,7 @@
         <v>181.57919999999999</v>
       </c>
     </row>
-    <row r="251" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>2017</v>
       </c>
@@ -9860,7 +9859,7 @@
         <v>423.97439999999995</v>
       </c>
     </row>
-    <row r="252" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>2017</v>
       </c>
@@ -9896,7 +9895,7 @@
         <v>363.30599999999998</v>
       </c>
     </row>
-    <row r="253" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>2017</v>
       </c>
@@ -9932,7 +9931,7 @@
         <v>242.1516</v>
       </c>
     </row>
-    <row r="254" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>2017</v>
       </c>
@@ -9968,7 +9967,7 @@
         <v>484.43639999999994</v>
       </c>
     </row>
-    <row r="255" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>2017</v>
       </c>
@@ -10004,7 +10003,7 @@
         <v>363.28559999999999</v>
       </c>
     </row>
-    <row r="256" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>2017</v>
       </c>
@@ -10040,7 +10039,7 @@
         <v>242.15480000000002</v>
       </c>
     </row>
-    <row r="257" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>2017</v>
       </c>
@@ -10076,7 +10075,7 @@
         <v>833.71309999999994</v>
       </c>
     </row>
-    <row r="258" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>2017</v>
       </c>
@@ -10112,7 +10111,7 @@
         <v>500.20960000000002</v>
       </c>
     </row>
-    <row r="259" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>2017</v>
       </c>
@@ -10148,7 +10147,7 @@
         <v>416.79800000000006</v>
       </c>
     </row>
-    <row r="260" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>2017</v>
       </c>
@@ -10184,7 +10183,7 @@
         <v>250.05920000000003</v>
       </c>
     </row>
-    <row r="261" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>2017</v>
       </c>
@@ -10220,7 +10219,7 @@
         <v>500.17860000000002</v>
       </c>
     </row>
-    <row r="262" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>2017</v>
       </c>
@@ -10256,7 +10255,7 @@
         <v>833.73439999999994</v>
       </c>
     </row>
-    <row r="263" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>2017</v>
       </c>
@@ -10292,7 +10291,7 @@
         <v>1098.6419999999998</v>
       </c>
     </row>
-    <row r="264" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>2017</v>
       </c>
@@ -10328,7 +10327,7 @@
         <v>411.95639999999997</v>
       </c>
     </row>
-    <row r="265" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>2017</v>
       </c>
@@ -10364,7 +10363,7 @@
         <v>1098.7014999999999</v>
       </c>
     </row>
-    <row r="266" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>2017</v>
       </c>
@@ -10400,7 +10399,7 @@
         <v>1098.9215999999999</v>
       </c>
     </row>
-    <row r="267" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>2017</v>
       </c>
@@ -10436,7 +10435,7 @@
         <v>416.8175</v>
       </c>
     </row>
-    <row r="268" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>2017</v>
       </c>
@@ -10472,7 +10471,7 @@
         <v>416.8381</v>
       </c>
     </row>
-    <row r="269" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>2017</v>
       </c>
@@ -10508,7 +10507,7 @@
         <v>71.972999999999999</v>
       </c>
     </row>
-    <row r="270" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>2017</v>
       </c>
@@ -10544,7 +10543,7 @@
         <v>612.89689999999996</v>
       </c>
     </row>
-    <row r="271" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>2017</v>
       </c>
@@ -10580,7 +10579,7 @@
         <v>781.48199999999997</v>
       </c>
     </row>
-    <row r="272" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>2017</v>
       </c>
@@ -10616,7 +10615,7 @@
         <v>1214.0625</v>
       </c>
     </row>
-    <row r="273" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>2017</v>
       </c>
@@ -10652,7 +10651,7 @@
         <v>849.80579999999998</v>
       </c>
     </row>
-    <row r="274" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>2017</v>
       </c>
@@ -10688,7 +10687,7 @@
         <v>849.80610000000001</v>
       </c>
     </row>
-    <row r="275" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>2017</v>
       </c>
@@ -10724,7 +10723,7 @@
         <v>1214.1357</v>
       </c>
     </row>
-    <row r="276" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>2017</v>
       </c>
@@ -10760,7 +10759,7 @@
         <v>606.99720000000002</v>
       </c>
     </row>
-    <row r="277" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>2017</v>
       </c>
@@ -10796,7 +10795,7 @@
         <v>486.15599999999995</v>
       </c>
     </row>
-    <row r="278" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>2017</v>
       </c>
@@ -10832,7 +10831,7 @@
         <v>781.47839999999997</v>
       </c>
     </row>
-    <row r="279" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>2017</v>
       </c>
@@ -10868,7 +10867,7 @@
         <v>520.94389999999999</v>
       </c>
     </row>
-    <row r="280" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>2017</v>
       </c>
@@ -10904,7 +10903,7 @@
         <v>260.4273</v>
       </c>
     </row>
-    <row r="281" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>2017</v>
       </c>
@@ -10940,7 +10939,7 @@
         <v>911.75909999999988</v>
       </c>
     </row>
-    <row r="282" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>2017</v>
       </c>
@@ -10976,7 +10975,7 @@
         <v>391.10399999999998</v>
       </c>
     </row>
-    <row r="283" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>2017</v>
       </c>
@@ -11012,7 +11011,7 @@
         <v>464.86799999999999</v>
       </c>
     </row>
-    <row r="284" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>2017</v>
       </c>
@@ -11048,7 +11047,7 @@
         <v>581.07999999999993</v>
       </c>
     </row>
-    <row r="285" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>2017</v>
       </c>
@@ -11084,7 +11083,7 @@
         <v>581.10739999999998</v>
       </c>
     </row>
-    <row r="286" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>2017</v>
       </c>
@@ -11120,7 +11119,7 @@
         <v>64.489999999999995</v>
       </c>
     </row>
-    <row r="287" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>2017</v>
       </c>
@@ -11156,7 +11155,7 @@
         <v>465.178</v>
       </c>
     </row>
-    <row r="288" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>2017</v>
       </c>
@@ -11192,7 +11191,7 @@
         <v>500.21040000000005</v>
       </c>
     </row>
-    <row r="289" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>2017</v>
       </c>
@@ -11228,7 +11227,7 @@
         <v>500.23980000000006</v>
       </c>
     </row>
-    <row r="290" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>2017</v>
       </c>
@@ -11264,7 +11263,7 @@
         <v>250.07049999999998</v>
       </c>
     </row>
-    <row r="291" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>2017</v>
       </c>
@@ -11300,7 +11299,7 @@
         <v>167.72600000000003</v>
       </c>
     </row>
-    <row r="292" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>2017</v>
       </c>
@@ -11336,7 +11335,7 @@
         <v>1858.7386999999999</v>
       </c>
     </row>
-    <row r="293" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>2017</v>
       </c>
@@ -11372,7 +11371,7 @@
         <v>302.72320000000002</v>
       </c>
     </row>
-    <row r="294" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>2017</v>
       </c>
@@ -11408,7 +11407,7 @@
         <v>242.15399999999997</v>
       </c>
     </row>
-    <row r="295" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>2017</v>
       </c>
@@ -11444,7 +11443,7 @@
         <v>851.56500000000005</v>
       </c>
     </row>
-    <row r="296" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>2017</v>
       </c>
@@ -11480,7 +11479,7 @@
         <v>3660.9122000000002</v>
       </c>
     </row>
-    <row r="297" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>2018</v>
       </c>
@@ -11516,7 +11515,7 @@
         <v>1652.3520000000001</v>
       </c>
     </row>
-    <row r="298" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>2018</v>
       </c>
@@ -11552,7 +11551,7 @@
         <v>2443.4180000000001</v>
       </c>
     </row>
-    <row r="299" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>2018</v>
       </c>
@@ -11588,7 +11587,7 @@
         <v>701.5598</v>
       </c>
     </row>
-    <row r="300" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>2018</v>
       </c>
@@ -11624,7 +11623,7 @@
         <v>801.88159999999993</v>
       </c>
     </row>
-    <row r="301" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>2018</v>
       </c>
@@ -11660,7 +11659,7 @@
         <v>726.36300000000006</v>
       </c>
     </row>
-    <row r="302" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>2018</v>
       </c>
@@ -11696,7 +11695,7 @@
         <v>1016.931</v>
       </c>
     </row>
-    <row r="303" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>2018</v>
       </c>
@@ -11732,7 +11731,7 @@
         <v>581.03560000000004</v>
       </c>
     </row>
-    <row r="304" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>2018</v>
       </c>
@@ -11768,7 +11767,7 @@
         <v>508.41909999999996</v>
       </c>
     </row>
-    <row r="305" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>2018</v>
       </c>
@@ -11804,7 +11803,7 @@
         <v>871.89010000000007</v>
       </c>
     </row>
-    <row r="306" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>2018</v>
       </c>
@@ -11840,7 +11839,7 @@
         <v>471.06180000000001</v>
       </c>
     </row>
-    <row r="307" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>2018</v>
       </c>
@@ -11876,7 +11875,7 @@
         <v>376.85420000000005</v>
       </c>
     </row>
-    <row r="308" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>2018</v>
       </c>
@@ -11912,7 +11911,7 @@
         <v>445.24800000000005</v>
       </c>
     </row>
-    <row r="309" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>2018</v>
       </c>
@@ -11948,7 +11947,7 @@
         <v>593.65949999999998</v>
       </c>
     </row>
-    <row r="310" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>2018</v>
       </c>
@@ -11984,7 +11983,7 @@
         <v>742.14560000000006</v>
       </c>
     </row>
-    <row r="311" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>2018</v>
       </c>
@@ -12020,7 +12019,7 @@
         <v>593.649</v>
       </c>
     </row>
-    <row r="312" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <v>2018</v>
       </c>
@@ -12056,7 +12055,7 @@
         <v>386.30800000000005</v>
       </c>
     </row>
-    <row r="313" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <v>2018</v>
       </c>
@@ -12092,7 +12091,7 @@
         <v>1159.0409999999999</v>
       </c>
     </row>
-    <row r="314" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>2018</v>
       </c>
@@ -12134,7 +12133,7 @@
         <v>296.80200000000002</v>
       </c>
     </row>
-    <row r="315" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>2018</v>
       </c>
@@ -12170,7 +12169,7 @@
         <v>1931.8732</v>
       </c>
     </row>
-    <row r="316" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
         <v>2018</v>
       </c>
@@ -12206,7 +12205,7 @@
         <v>2013.5844</v>
       </c>
     </row>
-    <row r="317" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
         <v>2018</v>
       </c>
@@ -12242,7 +12241,7 @@
         <v>384.90159999999997</v>
       </c>
     </row>
-    <row r="318" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>2018</v>
       </c>
@@ -12278,7 +12277,7 @@
         <v>288.61</v>
       </c>
     </row>
-    <row r="319" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>2018</v>
       </c>
@@ -12314,7 +12313,7 @@
         <v>288.64530000000002</v>
       </c>
     </row>
-    <row r="320" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>2018</v>
       </c>
@@ -12350,7 +12349,7 @@
         <v>96.15</v>
       </c>
     </row>
-    <row r="321" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>2018</v>
       </c>
@@ -12386,7 +12385,7 @@
         <v>288.6404</v>
       </c>
     </row>
-    <row r="322" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
         <v>2018</v>
       </c>
@@ -12458,7 +12457,7 @@
         <v>192.38040000000001</v>
       </c>
     </row>
-    <row r="324" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>2018</v>
       </c>
@@ -12494,7 +12493,7 @@
         <v>481.096</v>
       </c>
     </row>
-    <row r="325" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>2018</v>
       </c>
@@ -12530,7 +12529,7 @@
         <v>96.153199999999984</v>
       </c>
     </row>
-    <row r="326" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>2018</v>
       </c>
@@ -12566,7 +12565,7 @@
         <v>288.61379999999997</v>
       </c>
     </row>
-    <row r="327" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>2018</v>
       </c>
@@ -12602,7 +12601,7 @@
         <v>192.40920000000003</v>
       </c>
     </row>
-    <row r="328" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>2018</v>
       </c>
@@ -12638,7 +12637,7 @@
         <v>288.64079999999996</v>
       </c>
     </row>
-    <row r="329" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
         <v>2018</v>
       </c>
@@ -12674,7 +12673,7 @@
         <v>288.63159999999999</v>
       </c>
     </row>
-    <row r="330" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
         <v>2018</v>
       </c>
@@ -12710,7 +12709,7 @@
         <v>96.139999999999986</v>
       </c>
     </row>
-    <row r="331" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>2018</v>
       </c>
@@ -12746,7 +12745,7 @@
         <v>192.41839999999999</v>
       </c>
     </row>
-    <row r="332" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>2018</v>
       </c>
@@ -12782,7 +12781,7 @@
         <v>192.39979999999997</v>
       </c>
     </row>
-    <row r="333" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>2018</v>
       </c>
@@ -12818,7 +12817,7 @@
         <v>192.39339999999999</v>
       </c>
     </row>
-    <row r="334" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>2018</v>
       </c>
@@ -12854,7 +12853,7 @@
         <v>384.87059999999997</v>
       </c>
     </row>
-    <row r="335" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>2018</v>
       </c>
@@ -12890,7 +12889,7 @@
         <v>288.63159999999999</v>
       </c>
     </row>
-    <row r="336" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>2018</v>
       </c>
@@ -12926,7 +12925,7 @@
         <v>192.3888</v>
       </c>
     </row>
-    <row r="337" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>2018</v>
       </c>
@@ -12962,7 +12961,7 @@
         <v>1028.3779999999999</v>
       </c>
     </row>
-    <row r="338" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>2018</v>
       </c>
@@ -12998,7 +12997,7 @@
         <v>430.88580000000002</v>
       </c>
     </row>
-    <row r="339" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>2018</v>
       </c>
@@ -13034,7 +13033,7 @@
         <v>358.04640000000006</v>
       </c>
     </row>
-    <row r="340" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>2018</v>
       </c>
@@ -13070,7 +13069,7 @@
         <v>231.32990000000004</v>
       </c>
     </row>
-    <row r="341" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>2018</v>
       </c>
@@ -13106,7 +13105,7 @@
         <v>268.73099999999999</v>
       </c>
     </row>
-    <row r="342" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
         <v>2018</v>
       </c>
@@ -13142,7 +13141,7 @@
         <v>592.39729999999997</v>
       </c>
     </row>
-    <row r="343" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A343" s="1">
         <v>2018</v>
       </c>
@@ -13178,7 +13177,7 @@
         <v>571.30199999999991</v>
       </c>
     </row>
-    <row r="344" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
         <v>2018</v>
       </c>
@@ -13214,7 +13213,7 @@
         <v>285.6096</v>
       </c>
     </row>
-    <row r="345" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>2018</v>
       </c>
@@ -13250,7 +13249,7 @@
         <v>571.28329999999994</v>
       </c>
     </row>
-    <row r="346" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>2018</v>
       </c>
@@ -13286,7 +13285,7 @@
         <v>666.7056</v>
       </c>
     </row>
-    <row r="347" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A347" s="1">
         <v>2018</v>
       </c>
@@ -13322,7 +13321,7 @@
         <v>3529.4193000000005</v>
       </c>
     </row>
-    <row r="348" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A348" s="1">
         <v>2018</v>
       </c>
@@ -13358,7 +13357,7 @@
         <v>229.33199999999997</v>
       </c>
     </row>
-    <row r="349" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>2018</v>
       </c>
@@ -13394,7 +13393,7 @@
         <v>288.16759999999999</v>
       </c>
     </row>
-    <row r="350" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>2018</v>
       </c>
@@ -13430,7 +13429,7 @@
         <v>63.863999999999997</v>
       </c>
     </row>
-    <row r="351" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>2018</v>
       </c>
@@ -13466,7 +13465,7 @@
         <v>447.09610000000004</v>
       </c>
     </row>
-    <row r="352" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>2018</v>
       </c>
@@ -13502,7 +13501,7 @@
         <v>619.00800000000004</v>
       </c>
     </row>
-    <row r="353" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>2018</v>
       </c>
@@ -13538,7 +13537,7 @@
         <v>1010.3589999999999</v>
       </c>
     </row>
-    <row r="354" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>2018</v>
       </c>
@@ -13574,7 +13573,7 @@
         <v>707.26220000000001</v>
       </c>
     </row>
-    <row r="355" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>2018</v>
       </c>
@@ -13610,7 +13609,7 @@
         <v>707.29489999999998</v>
       </c>
     </row>
-    <row r="356" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>2018</v>
       </c>
@@ -13646,7 +13645,7 @@
         <v>1010.4198</v>
       </c>
     </row>
-    <row r="357" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>2018</v>
       </c>
@@ -13682,7 +13681,7 @@
         <v>505.1848</v>
       </c>
     </row>
-    <row r="358" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>2018</v>
       </c>
@@ -13718,7 +13717,7 @@
         <v>404.55</v>
       </c>
     </row>
-    <row r="359" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>2018</v>
       </c>
@@ -13754,7 +13753,7 @@
         <v>722.15740000000005</v>
       </c>
     </row>
-    <row r="360" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>2018</v>
       </c>
@@ -13790,7 +13789,7 @@
         <v>412.62270000000001</v>
       </c>
     </row>
-    <row r="361" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>2018</v>
       </c>
@@ -13826,7 +13825,7 @@
         <v>309.4119</v>
       </c>
     </row>
-    <row r="362" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>2018</v>
       </c>
@@ -13862,7 +13861,7 @@
         <v>825.34199999999998</v>
       </c>
     </row>
-    <row r="363" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>2018</v>
       </c>
@@ -13898,7 +13897,7 @@
         <v>309.43</v>
       </c>
     </row>
-    <row r="364" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A364" s="1">
         <v>2018</v>
       </c>
@@ -13934,7 +13933,7 @@
         <v>376.84500000000003</v>
       </c>
     </row>
-    <row r="365" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A365" s="1">
         <v>2018</v>
       </c>
@@ -13970,7 +13969,7 @@
         <v>471.06900000000002</v>
       </c>
     </row>
-    <row r="366" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>2018</v>
       </c>
@@ -14006,7 +14005,7 @@
         <v>376.84219999999993</v>
       </c>
     </row>
-    <row r="367" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>2018</v>
       </c>
@@ -14042,7 +14041,7 @@
         <v>377.06760000000003</v>
       </c>
     </row>
-    <row r="368" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>2018</v>
       </c>
@@ -14078,7 +14077,7 @@
         <v>845.10720000000003</v>
       </c>
     </row>
-    <row r="369" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A369" s="1">
         <v>2018</v>
       </c>
@@ -14114,7 +14113,7 @@
         <v>886.60800000000006</v>
       </c>
     </row>
-    <row r="370" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A370" s="1">
         <v>2018</v>
       </c>
@@ -14150,7 +14149,7 @@
         <v>317.06490000000002</v>
       </c>
     </row>
-    <row r="371" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
         <v>2018</v>
       </c>
@@ -14186,7 +14185,7 @@
         <v>245.85600000000002</v>
       </c>
     </row>
-    <row r="372" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>2018</v>
       </c>
@@ -14222,7 +14221,7 @@
         <v>1113.5696</v>
       </c>
     </row>
-    <row r="373" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A373" s="1">
         <v>2018</v>
       </c>
@@ -14258,7 +14257,7 @@
         <v>192.4</v>
       </c>
     </row>
-    <row r="374" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A374" s="1">
         <v>2018</v>
       </c>
@@ -14294,7 +14293,7 @@
         <v>194.46899999999999</v>
       </c>
     </row>
-    <row r="375" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
         <v>2018</v>
       </c>
@@ -14330,7 +14329,7 @@
         <v>543.36749999999995</v>
       </c>
     </row>
-    <row r="376" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>2018</v>
       </c>
@@ -14366,7 +14365,7 @@
         <v>4644.2929999999997</v>
       </c>
     </row>
-    <row r="377" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>2019</v>
       </c>
@@ -14402,7 +14401,7 @@
         <v>1874.6623999999999</v>
       </c>
     </row>
-    <row r="378" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>2019</v>
       </c>
@@ -14438,7 +14437,7 @@
         <v>2669.9827999999998</v>
       </c>
     </row>
-    <row r="379" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>2019</v>
       </c>
@@ -14474,7 +14473,7 @@
         <v>83.158799999999999</v>
       </c>
     </row>
-    <row r="380" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>2019</v>
       </c>
@@ -14510,7 +14509,7 @@
         <v>19.032</v>
       </c>
     </row>
-    <row r="381" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>2019</v>
       </c>
@@ -14546,7 +14545,7 @@
         <v>785.56500000000005</v>
       </c>
     </row>
-    <row r="382" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>2019</v>
       </c>
@@ -14582,7 +14581,7 @@
         <v>1178.337</v>
       </c>
     </row>
-    <row r="383" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A383" s="1">
         <v>2019</v>
       </c>
@@ -14618,7 +14617,7 @@
         <v>687.32260000000008</v>
       </c>
     </row>
-    <row r="384" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A384" s="1">
         <v>2019</v>
       </c>
@@ -14654,7 +14653,7 @@
         <v>589.13869999999997</v>
       </c>
     </row>
-    <row r="385" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A385" s="1">
         <v>2019</v>
       </c>
@@ -14690,7 +14689,7 @@
         <v>982.40530000000001</v>
       </c>
     </row>
-    <row r="386" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
         <v>2019</v>
       </c>
@@ -14726,7 +14725,7 @@
         <v>288.8999</v>
       </c>
     </row>
-    <row r="387" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A387" s="1">
         <v>2019</v>
       </c>
@@ -14762,7 +14761,7 @@
         <v>231.08940000000001</v>
       </c>
     </row>
-    <row r="388" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A388" s="1">
         <v>2019</v>
       </c>
@@ -14798,7 +14797,7 @@
         <v>182.376</v>
       </c>
     </row>
-    <row r="389" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A389" s="1">
         <v>2019</v>
       </c>
@@ -14834,7 +14833,7 @@
         <v>533.476</v>
       </c>
     </row>
-    <row r="390" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A390" s="1">
         <v>2019</v>
       </c>
@@ -14870,7 +14869,7 @@
         <v>1211.8792000000001</v>
       </c>
     </row>
-    <row r="391" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A391" s="1">
         <v>2019</v>
       </c>
@@ -14906,7 +14905,7 @@
         <v>892.93049999999994</v>
       </c>
     </row>
-    <row r="392" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A392" s="1">
         <v>2019</v>
       </c>
@@ -14942,7 +14941,7 @@
         <v>211.1584</v>
       </c>
     </row>
-    <row r="393" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A393" s="1">
         <v>2019</v>
       </c>
@@ -14978,7 +14977,7 @@
         <v>437.63200000000001</v>
       </c>
     </row>
-    <row r="394" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A394" s="1">
         <v>2019</v>
       </c>
@@ -15020,7 +15019,7 @@
         <v>170.42850000000001</v>
       </c>
     </row>
-    <row r="395" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A395" s="1">
         <v>2019</v>
       </c>
@@ -15056,7 +15055,7 @@
         <v>596.74760000000003</v>
       </c>
     </row>
-    <row r="396" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A396" s="1">
         <v>2019</v>
       </c>
@@ -15092,7 +15091,7 @@
         <v>2469.5279999999998</v>
       </c>
     </row>
-    <row r="397" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A397" s="1">
         <v>2019</v>
       </c>
@@ -15128,7 +15127,7 @@
         <v>1874.9947999999997</v>
       </c>
     </row>
-    <row r="398" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A398" s="1">
         <v>2019</v>
       </c>
@@ -15164,7 +15163,7 @@
         <v>1770.7984999999999</v>
       </c>
     </row>
-    <row r="399" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A399" s="1">
         <v>2019</v>
       </c>
@@ -15200,7 +15199,7 @@
         <v>1055.6790000000001</v>
       </c>
     </row>
-    <row r="400" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A400" s="1">
         <v>2019</v>
       </c>
@@ -15236,7 +15235,7 @@
         <v>552.6803000000001</v>
       </c>
     </row>
-    <row r="401" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>2019</v>
       </c>
@@ -15272,7 +15271,7 @@
         <v>276.33050000000003</v>
       </c>
     </row>
-    <row r="402" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A402" s="1">
         <v>2019</v>
       </c>
@@ -15308,7 +15307,7 @@
         <v>460.55490000000003</v>
       </c>
     </row>
-    <row r="403" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
         <v>2019</v>
       </c>
@@ -15344,7 +15343,7 @@
         <v>737.03840000000002</v>
       </c>
     </row>
-    <row r="404" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A404" s="1">
         <v>2019</v>
       </c>
@@ -15380,7 +15379,7 @@
         <v>387.39599999999996</v>
       </c>
     </row>
-    <row r="405" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
         <v>2019</v>
       </c>
@@ -15416,7 +15415,7 @@
         <v>193.69799999999998</v>
       </c>
     </row>
-    <row r="406" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A406" s="1">
         <v>2019</v>
       </c>
@@ -15452,7 +15451,7 @@
         <v>322.81809999999996</v>
       </c>
     </row>
-    <row r="407" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A407" s="1">
         <v>2019</v>
       </c>
@@ -15488,7 +15487,7 @@
         <v>322.91999999999996</v>
       </c>
     </row>
-    <row r="408" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A408" s="1">
         <v>2019</v>
       </c>
@@ -15524,7 +15523,7 @@
         <v>6684.4049999999997</v>
       </c>
     </row>
-    <row r="409" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A409" s="1">
         <v>2019</v>
       </c>
@@ -15560,7 +15559,7 @@
         <v>552.70330000000001</v>
       </c>
     </row>
-    <row r="410" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
         <v>2019</v>
       </c>
@@ -15596,7 +15595,7 @@
         <v>552.70600000000002</v>
       </c>
     </row>
-    <row r="411" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
         <v>2019</v>
       </c>
@@ -15632,7 +15631,7 @@
         <v>64.08</v>
       </c>
     </row>
-    <row r="412" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A412" s="1">
         <v>2019</v>
       </c>
@@ -15668,7 +15667,7 @@
         <v>418.79310000000004</v>
       </c>
     </row>
-    <row r="413" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A413" s="1">
         <v>2019</v>
       </c>
@@ -15704,7 +15703,7 @@
         <v>434.53800000000001</v>
       </c>
     </row>
-    <row r="414" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A414" s="1">
         <v>2019</v>
       </c>
@@ -15740,7 +15739,7 @@
         <v>873.47749999999996</v>
       </c>
     </row>
-    <row r="415" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A415" s="1">
         <v>2019</v>
       </c>
@@ -15776,7 +15775,7 @@
         <v>611.39599999999996</v>
       </c>
     </row>
-    <row r="416" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A416" s="1">
         <v>2019</v>
       </c>
@@ -15812,7 +15811,7 @@
         <v>611.39519999999993</v>
       </c>
     </row>
-    <row r="417" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A417" s="1">
         <v>2019</v>
       </c>
@@ -15848,7 +15847,7 @@
         <v>960.77009999999996</v>
       </c>
     </row>
-    <row r="418" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A418" s="1">
         <v>2019</v>
       </c>
@@ -15884,7 +15883,7 @@
         <v>523.99639999999999</v>
       </c>
     </row>
-    <row r="419" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A419" s="1">
         <v>2019</v>
       </c>
@@ -15920,7 +15919,7 @@
         <v>437.08799999999997</v>
       </c>
     </row>
-    <row r="420" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A420" s="1">
         <v>2019</v>
       </c>
@@ -15956,7 +15955,7 @@
         <v>487.125</v>
       </c>
     </row>
-    <row r="421" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A421" s="1">
         <v>2019</v>
       </c>
@@ -15992,7 +15991,7 @@
         <v>393.53700000000003</v>
       </c>
     </row>
-    <row r="422" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A422" s="1">
         <v>2019</v>
       </c>
@@ -16028,7 +16027,7 @@
         <v>319.84440000000001</v>
       </c>
     </row>
-    <row r="423" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A423" s="1">
         <v>2019</v>
       </c>
@@ -16064,7 +16063,7 @@
         <v>844.30499999999995</v>
       </c>
     </row>
-    <row r="424" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A424" s="1">
         <v>2019</v>
       </c>
@@ -16100,7 +16099,7 @@
         <v>231.636</v>
       </c>
     </row>
-    <row r="425" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A425" s="1">
         <v>2019</v>
       </c>
@@ -16136,7 +16135,7 @@
         <v>288.8775</v>
       </c>
     </row>
-    <row r="426" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A426" s="1">
         <v>2019</v>
       </c>
@@ -16172,7 +16171,7 @@
         <v>346.67700000000002</v>
       </c>
     </row>
-    <row r="427" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A427" s="1">
         <v>2019</v>
       </c>
@@ -16208,7 +16207,7 @@
         <v>288.84559999999999</v>
       </c>
     </row>
-    <row r="428" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A428" s="1">
         <v>2019</v>
       </c>
@@ -16244,7 +16243,7 @@
         <v>289.05239999999998</v>
       </c>
     </row>
-    <row r="429" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A429" s="1">
         <v>2019</v>
       </c>
@@ -16280,7 +16279,7 @@
         <v>276.74299999999999</v>
       </c>
     </row>
-    <row r="430" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A430" s="1">
         <v>2019</v>
       </c>
@@ -16316,7 +16315,7 @@
         <v>2342.6597999999999</v>
       </c>
     </row>
-    <row r="431" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A431" s="1">
         <v>2019</v>
       </c>
@@ -16352,7 +16351,7 @@
         <v>3528.614</v>
       </c>
     </row>
-    <row r="432" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A432" s="1">
         <v>2019</v>
       </c>
@@ -16388,7 +16387,7 @@
         <v>8017.0802999999996</v>
       </c>
     </row>
-    <row r="433" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A433" s="1">
         <v>2020</v>
       </c>
@@ -16424,7 +16423,7 @@
         <v>1488.1152000000002</v>
       </c>
     </row>
-    <row r="434" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A434" s="1">
         <v>2020</v>
       </c>
@@ -16460,7 +16459,7 @@
         <v>2193.8044</v>
       </c>
     </row>
-    <row r="435" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A435" s="1">
         <v>2020</v>
       </c>
@@ -16496,7 +16495,7 @@
         <v>88.170500000000004</v>
       </c>
     </row>
-    <row r="436" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A436" s="1">
         <v>2020</v>
       </c>
@@ -16532,7 +16531,7 @@
         <v>1280.634</v>
       </c>
     </row>
-    <row r="437" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A437" s="1">
         <v>2020</v>
       </c>
@@ -16568,7 +16567,7 @@
         <v>698.10100000000011</v>
       </c>
     </row>
-    <row r="438" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A438" s="1">
         <v>2020</v>
       </c>
@@ -16604,7 +16603,7 @@
         <v>342.71899999999999</v>
       </c>
     </row>
-    <row r="439" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A439" s="1">
         <v>2020</v>
       </c>
@@ -16640,7 +16639,7 @@
         <v>248.0052</v>
       </c>
     </row>
-    <row r="440" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A440" s="1">
         <v>2020</v>
       </c>
@@ -16676,7 +16675,7 @@
         <v>415.08</v>
       </c>
     </row>
-    <row r="441" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A441" s="1">
         <v>2020</v>
       </c>
@@ -16712,7 +16711,7 @@
         <v>631.37699999999995</v>
       </c>
     </row>
-    <row r="442" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A442" s="1">
         <v>2020</v>
       </c>
@@ -16748,7 +16747,7 @@
         <v>544.7924999999999</v>
       </c>
     </row>
-    <row r="443" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A443" s="1">
         <v>2020</v>
       </c>
@@ -16784,7 +16783,7 @@
         <v>390.98390000000001</v>
       </c>
     </row>
-    <row r="444" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A444" s="1">
         <v>2020</v>
       </c>
@@ -16820,7 +16819,7 @@
         <v>1176.0045000000002</v>
       </c>
     </row>
-    <row r="445" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A445" s="1">
         <v>2020</v>
       </c>
@@ -16862,7 +16861,7 @@
         <v>285.26850000000002</v>
       </c>
     </row>
-    <row r="446" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A446" s="1">
         <v>2020</v>
       </c>
@@ -16898,7 +16897,7 @@
         <v>1931.0095999999999</v>
       </c>
     </row>
-    <row r="447" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A447" s="1">
         <v>2020</v>
       </c>
@@ -16934,7 +16933,7 @@
         <v>1786.6116000000002</v>
       </c>
     </row>
-    <row r="448" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A448" s="1">
         <v>2020</v>
       </c>
@@ -16970,7 +16969,7 @@
         <v>2664.4555</v>
       </c>
     </row>
-    <row r="449" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A449" s="1">
         <v>2020</v>
       </c>
@@ -17006,7 +17005,7 @@
         <v>367.488</v>
       </c>
     </row>
-    <row r="450" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A450" s="1">
         <v>2020</v>
       </c>
@@ -17042,7 +17041,7 @@
         <v>3548.5589999999997</v>
       </c>
     </row>
-    <row r="451" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A451" s="1">
         <v>2020</v>
       </c>
@@ -17078,7 +17077,7 @@
         <v>3702.8397000000004</v>
       </c>
     </row>
-    <row r="452" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A452" s="1">
         <v>2020</v>
       </c>
@@ -17114,7 +17113,7 @@
         <v>695.19310000000007</v>
       </c>
     </row>
-    <row r="453" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A453" s="1">
         <v>2020</v>
       </c>
@@ -17150,7 +17149,7 @@
         <v>752.19240000000002</v>
       </c>
     </row>
-    <row r="454" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A454" s="1">
         <v>2020</v>
       </c>
@@ -17186,7 +17185,7 @@
         <v>412.24949999999995</v>
       </c>
     </row>
-    <row r="455" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A455" s="1">
         <v>2020</v>
       </c>
@@ -17222,7 +17221,7 @@
         <v>412.08630000000005</v>
       </c>
     </row>
-    <row r="456" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A456" s="1">
         <v>2020</v>
       </c>
@@ -17258,7 +17257,7 @@
         <v>223.99740000000003</v>
       </c>
     </row>
-    <row r="457" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A457" s="1">
         <v>2020</v>
       </c>
@@ -17294,7 +17293,7 @@
         <v>4381.3459000000003</v>
       </c>
     </row>
-    <row r="458" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A458" s="1">
         <v>2020</v>
       </c>
@@ -17330,7 +17329,7 @@
         <v>501.774</v>
       </c>
     </row>
-    <row r="459" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A459" s="1">
         <v>2020</v>
       </c>
@@ -17366,7 +17365,7 @@
         <v>833.20299999999997</v>
       </c>
     </row>
-    <row r="460" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A460" s="1">
         <v>2020</v>
       </c>
@@ -17402,7 +17401,7 @@
         <v>558.03719999999998</v>
       </c>
     </row>
-    <row r="461" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A461" s="1">
         <v>2020</v>
       </c>
@@ -17438,7 +17437,7 @@
         <v>593.48900000000003</v>
       </c>
     </row>
-    <row r="462" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A462" s="1">
         <v>2020</v>
       </c>
@@ -17474,7 +17473,7 @@
         <v>889.54559999999992</v>
       </c>
     </row>
-    <row r="463" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A463" s="1">
         <v>2020</v>
       </c>
@@ -17510,7 +17509,7 @@
         <v>461.53039999999999</v>
       </c>
     </row>
-    <row r="464" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A464" s="1">
         <v>2020</v>
       </c>
@@ -17546,7 +17545,7 @@
         <v>373.05599999999993</v>
       </c>
     </row>
-    <row r="465" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A465" s="1">
         <v>2020</v>
       </c>
@@ -17582,7 +17581,7 @@
         <v>556.45450000000005</v>
       </c>
     </row>
-    <row r="466" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A466" s="1">
         <v>2020</v>
       </c>
@@ -17618,7 +17617,7 @@
         <v>361.78380000000004</v>
       </c>
     </row>
-    <row r="467" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A467" s="1">
         <v>2020</v>
       </c>
@@ -17654,7 +17653,7 @@
         <v>206.49930000000001</v>
       </c>
     </row>
-    <row r="468" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A468" s="1">
         <v>2020</v>
       </c>
@@ -17690,7 +17689,7 @@
         <v>580.62899999999991</v>
       </c>
     </row>
-    <row r="469" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A469" s="1">
         <v>2020</v>
       </c>
@@ -17726,7 +17725,7 @@
         <v>249.13479999999996</v>
       </c>
     </row>
-    <row r="470" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A470" s="1">
         <v>2020</v>
       </c>
@@ -17762,7 +17761,7 @@
         <v>296.03700000000003</v>
       </c>
     </row>
-    <row r="471" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A471" s="1">
         <v>2020</v>
       </c>
@@ -17798,7 +17797,7 @@
         <v>389.38200000000001</v>
       </c>
     </row>
-    <row r="472" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A472" s="1">
         <v>2020</v>
       </c>
@@ -17834,7 +17833,7 @@
         <v>314.70269999999999</v>
       </c>
     </row>
-    <row r="473" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A473" s="1">
         <v>2020</v>
       </c>
@@ -17870,7 +17869,7 @@
         <v>290.69040000000001</v>
       </c>
     </row>
-    <row r="474" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A474" s="1">
         <v>2020</v>
       </c>
@@ -17906,7 +17905,7 @@
         <v>418.70220000000006</v>
       </c>
     </row>
-    <row r="475" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A475" s="1">
         <v>2020</v>
       </c>
@@ -17942,7 +17941,7 @@
         <v>450.74880000000007</v>
       </c>
     </row>
-    <row r="476" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A476" s="1">
         <v>2020</v>
       </c>
@@ -17978,7 +17977,7 @@
         <v>179.99169999999998</v>
       </c>
     </row>
-    <row r="477" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A477" s="1">
         <v>2020</v>
       </c>
@@ -18014,7 +18013,7 @@
         <v>142.09299999999999</v>
       </c>
     </row>
-    <row r="478" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A478" s="1">
         <v>2020</v>
       </c>
@@ -18050,7 +18049,7 @@
         <v>1178.2692999999999</v>
       </c>
     </row>
-    <row r="479" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A479" s="1">
         <v>2020</v>
       </c>
@@ -18086,7 +18085,7 @@
         <v>2368.1927999999998</v>
       </c>
     </row>
-    <row r="480" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A480" s="1">
         <v>2020</v>
       </c>
@@ -18122,7 +18121,7 @@
         <v>9543.7278000000006</v>
       </c>
     </row>
-    <row r="481" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A481" s="1">
         <v>2020</v>
       </c>
@@ -18158,7 +18157,7 @@
         <v>2990.2674000000006</v>
       </c>
     </row>
-    <row r="482" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A482" s="1">
         <v>2020</v>
       </c>
@@ -18194,7 +18193,7 @@
         <v>1637.6880000000001</v>
       </c>
     </row>
-    <row r="483" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A483" s="1">
         <v>2020</v>
       </c>
@@ -18230,7 +18229,7 @@
         <v>3988.8899999999994</v>
       </c>
     </row>
-    <row r="484" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A484" s="1">
         <v>2021</v>
       </c>
@@ -18266,7 +18265,7 @@
         <v>1064.5425</v>
       </c>
     </row>
-    <row r="485" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A485" s="1">
         <v>2021</v>
       </c>
@@ -18302,7 +18301,7 @@
         <v>1503.2015999999999</v>
       </c>
     </row>
-    <row r="486" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A486" s="1">
         <v>2021</v>
       </c>
@@ -18338,7 +18337,7 @@
         <v>2151.4639999999999</v>
       </c>
     </row>
-    <row r="487" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A487" s="1">
         <v>2021</v>
       </c>
@@ -18374,7 +18373,7 @@
         <v>529.18039999999996</v>
       </c>
     </row>
-    <row r="488" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A488" s="1">
         <v>2021</v>
       </c>
@@ -18410,7 +18409,7 @@
         <v>259.00040000000001</v>
       </c>
     </row>
-    <row r="489" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A489" s="1">
         <v>2021</v>
       </c>
@@ -18446,7 +18445,7 @@
         <v>187.42519999999999</v>
       </c>
     </row>
-    <row r="490" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A490" s="1">
         <v>2021</v>
       </c>
@@ -18482,7 +18481,7 @@
         <v>289.584</v>
       </c>
     </row>
-    <row r="491" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A491" s="1">
         <v>2021</v>
       </c>
@@ -18518,7 +18517,7 @@
         <v>784.89749999999992</v>
       </c>
     </row>
-    <row r="492" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A492" s="1">
         <v>2021</v>
       </c>
@@ -18554,7 +18553,7 @@
         <v>513.88349999999991</v>
       </c>
     </row>
-    <row r="493" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A493" s="1">
         <v>2021</v>
       </c>
@@ -18590,7 +18589,7 @@
         <v>500.3775</v>
       </c>
     </row>
-    <row r="494" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A494" s="1">
         <v>2021</v>
       </c>
@@ -18626,7 +18625,7 @@
         <v>125.72490000000001</v>
       </c>
     </row>
-    <row r="495" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A495" s="1">
         <v>2021</v>
       </c>
@@ -18662,7 +18661,7 @@
         <v>377.93099999999998</v>
       </c>
     </row>
-    <row r="496" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A496" s="1">
         <v>2021</v>
       </c>
@@ -18704,7 +18703,7 @@
         <v>318.53249999999997</v>
       </c>
     </row>
-    <row r="497" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A497" s="1">
         <v>2021</v>
       </c>
@@ -18740,7 +18739,7 @@
         <v>377.93099999999998</v>
       </c>
     </row>
-    <row r="498" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A498" s="1">
         <v>2021</v>
       </c>
@@ -18776,7 +18775,7 @@
         <v>1350.2483999999999</v>
       </c>
     </row>
-    <row r="499" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A499" s="1">
         <v>2021</v>
       </c>
@@ -18812,7 +18811,7 @@
         <v>438.50940000000003</v>
       </c>
     </row>
-    <row r="500" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A500" s="1">
         <v>2021</v>
       </c>
@@ -18848,7 +18847,7 @@
         <v>1404.2343000000001</v>
       </c>
     </row>
-    <row r="501" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A501" s="1">
         <v>2021</v>
       </c>
@@ -18884,7 +18883,7 @@
         <v>1008.1407999999999</v>
       </c>
     </row>
-    <row r="502" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A502" s="1">
         <v>2021</v>
       </c>
@@ -18920,7 +18919,7 @@
         <v>1444.702</v>
       </c>
     </row>
-    <row r="503" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A503" s="1">
         <v>2021</v>
       </c>
@@ -18956,7 +18955,7 @@
         <v>1507.7334000000001</v>
       </c>
     </row>
-    <row r="504" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A504" s="1">
         <v>2021</v>
       </c>
@@ -18992,7 +18991,7 @@
         <v>33.370399999999997</v>
       </c>
     </row>
-    <row r="505" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A505" s="1">
         <v>2021</v>
       </c>
@@ -19028,7 +19027,7 @@
         <v>870.13400000000001</v>
       </c>
     </row>
-    <row r="506" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A506" s="1">
         <v>2021</v>
       </c>
@@ -19064,7 +19063,7 @@
         <v>1265.6324999999999</v>
       </c>
     </row>
-    <row r="507" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A507" s="1">
         <v>2021</v>
       </c>
@@ -19100,7 +19099,7 @@
         <v>1594.0342000000001</v>
       </c>
     </row>
-    <row r="508" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A508" s="1">
         <v>2021</v>
       </c>
@@ -19136,7 +19135,7 @@
         <v>2387.8539999999998</v>
       </c>
     </row>
-    <row r="509" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A509" s="1">
         <v>2021</v>
       </c>
@@ -19172,7 +19171,7 @@
         <v>3076.2954</v>
       </c>
     </row>
-    <row r="510" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A510" s="1">
         <v>2021</v>
       </c>
@@ -19208,7 +19207,7 @@
         <v>93.951000000000008</v>
       </c>
     </row>
-    <row r="511" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A511" s="1">
         <v>2021</v>
       </c>
@@ -19244,7 +19243,7 @@
         <v>953.17200000000014</v>
       </c>
     </row>
-    <row r="512" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A512" s="1">
         <v>2021</v>
       </c>
@@ -19280,7 +19279,7 @@
         <v>910.25549999999998</v>
       </c>
     </row>
-    <row r="513" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A513" s="1">
         <v>2021</v>
       </c>
@@ -19316,7 +19315,7 @@
         <v>585.63959999999997</v>
       </c>
     </row>
-    <row r="514" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A514" s="1">
         <v>2021</v>
       </c>
@@ -19352,7 +19351,7 @@
         <v>480.14460000000003</v>
       </c>
     </row>
-    <row r="515" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A515" s="1">
         <v>2021</v>
       </c>
@@ -19388,7 +19387,7 @@
         <v>378.80369999999999</v>
       </c>
     </row>
-    <row r="516" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A516" s="1">
         <v>2021</v>
       </c>
@@ -19424,7 +19423,7 @@
         <v>473.59279999999995</v>
       </c>
     </row>
-    <row r="517" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A517" s="1">
         <v>2021</v>
       </c>
@@ -19460,7 +19459,7 @@
         <v>383.20599999999996</v>
       </c>
     </row>
-    <row r="518" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A518" s="1">
         <v>2021</v>
       </c>
@@ -19496,7 +19495,7 @@
         <v>223.6095</v>
       </c>
     </row>
-    <row r="519" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A519" s="1">
         <v>2021</v>
       </c>
@@ -19532,7 +19531,7 @@
         <v>237.3081</v>
       </c>
     </row>
-    <row r="520" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A520" s="1">
         <v>2021</v>
       </c>
@@ -19568,7 +19567,7 @@
         <v>219.76499999999999</v>
       </c>
     </row>
-    <row r="521" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A521" s="1">
         <v>2021</v>
       </c>
@@ -19604,7 +19603,7 @@
         <v>373.19279999999998</v>
       </c>
     </row>
-    <row r="522" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A522" s="1">
         <v>2021</v>
       </c>
@@ -19640,7 +19639,7 @@
         <v>401.68080000000003</v>
       </c>
     </row>
-    <row r="523" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A523" s="1">
         <v>2021</v>
       </c>
@@ -19676,7 +19675,7 @@
         <v>160.4794</v>
       </c>
     </row>
-    <row r="524" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A524" s="1">
         <v>2021</v>
       </c>
@@ -19712,7 +19711,7 @@
         <v>126.35199999999999</v>
       </c>
     </row>
-    <row r="525" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A525" s="1">
         <v>2021</v>
       </c>
@@ -19748,7 +19747,7 @@
         <v>1014.3770000000001</v>
       </c>
     </row>
-    <row r="526" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A526" s="1">
         <v>2021</v>
       </c>
@@ -19784,7 +19783,7 @@
         <v>8161.5060000000012</v>
       </c>
     </row>
-    <row r="527" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A527" s="1">
         <v>2021</v>
       </c>
@@ -19820,7 +19819,7 @@
         <v>1993.1720000000003</v>
       </c>
     </row>
-    <row r="528" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A528" s="1">
         <v>2021</v>
       </c>
@@ -19856,7 +19855,7 @@
         <v>3841.5260000000003</v>
       </c>
     </row>
-    <row r="529" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A529" s="1">
         <v>2021</v>
       </c>
@@ -19892,7 +19891,7 @@
         <v>2627.6489999999999</v>
       </c>
     </row>
-    <row r="530" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A530" s="1">
         <v>2021</v>
       </c>
@@ -19928,7 +19927,7 @@
         <v>792.18280000000004</v>
       </c>
     </row>
-    <row r="531" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A531" s="1">
         <v>2021</v>
       </c>
@@ -19964,7 +19963,7 @@
         <v>491.65600000000006</v>
       </c>
     </row>
-    <row r="532" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A532" s="1">
         <v>2021</v>
       </c>
@@ -20000,7 +19999,7 @@
         <v>1225.3050999999998</v>
       </c>
     </row>
-    <row r="533" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A533" s="1">
         <v>2021</v>
       </c>
@@ -20036,7 +20035,7 @@
         <v>2000.6840999999999</v>
       </c>
     </row>
-    <row r="534" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A534" s="1">
         <v>2021</v>
       </c>
@@ -20072,7 +20071,7 @@
         <v>1265.192</v>
       </c>
     </row>
-    <row r="535" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A535" s="1">
         <v>2021</v>
       </c>
@@ -20108,7 +20107,7 @@
         <v>1603.8190000000002</v>
       </c>
     </row>
-    <row r="536" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A536" s="1">
         <v>2021</v>
       </c>
@@ -20144,7 +20143,7 @@
         <v>1770.4650000000001</v>
       </c>
     </row>
-    <row r="537" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A537" s="1">
         <v>2021</v>
       </c>
@@ -20180,7 +20179,7 @@
         <v>774.65359999999998</v>
       </c>
     </row>
-    <row r="538" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A538" s="1">
         <v>2021</v>
       </c>
@@ -20216,7 +20215,7 @@
         <v>1291.3488</v>
       </c>
     </row>
-    <row r="539" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A539" s="1">
         <v>2021</v>
       </c>
@@ -20252,7 +20251,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="540" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A540" s="1">
         <v>2022</v>
       </c>
@@ -20288,7 +20287,7 @@
         <v>748.80000000000007</v>
       </c>
     </row>
-    <row r="541" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A541" s="1">
         <v>2022</v>
       </c>
@@ -20324,7 +20323,7 @@
         <v>1000.8</v>
       </c>
     </row>
-    <row r="542" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A542" s="1">
         <v>2022</v>
       </c>
@@ -20360,7 +20359,7 @@
         <v>1957.0000000000002</v>
       </c>
     </row>
-    <row r="543" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A543" s="1">
         <v>2022</v>
       </c>
@@ -20399,7 +20398,7 @@
         <v>5775.9</v>
       </c>
     </row>
-    <row r="544" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A544" s="1">
         <v>2022</v>
       </c>
@@ -20435,7 +20434,7 @@
         <v>1067.97</v>
       </c>
     </row>
-    <row r="545" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A545" s="1">
         <v>2022</v>
       </c>
@@ -20474,7 +20473,7 @@
         <v>329.40000000000003</v>
       </c>
     </row>
-    <row r="546" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A546" s="1">
         <v>2022</v>
       </c>
@@ -20513,7 +20512,7 @@
         <v>195.29999999999998</v>
       </c>
     </row>
-    <row r="547" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A547" s="1">
         <v>2022</v>
       </c>
@@ -20552,7 +20551,7 @@
         <v>340.2</v>
       </c>
     </row>
-    <row r="548" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A548" s="1">
         <v>2022</v>
       </c>
@@ -20588,7 +20587,7 @@
         <v>1030.5</v>
       </c>
     </row>
-    <row r="549" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A549" s="1">
         <v>2022</v>
       </c>
@@ -20627,7 +20626,7 @@
         <v>468.9</v>
       </c>
     </row>
-    <row r="550" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A550" s="1">
         <v>2022</v>
       </c>
@@ -20666,7 +20665,7 @@
         <v>432.9</v>
       </c>
     </row>
-    <row r="551" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A551" s="1">
         <v>2022</v>
       </c>
@@ -20702,7 +20701,7 @@
         <v>196.65</v>
       </c>
     </row>
-    <row r="552" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A552" s="1">
         <v>2022</v>
       </c>
@@ -20738,7 +20737,7 @@
         <v>565.45000000000005</v>
       </c>
     </row>
-    <row r="553" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A553" s="1">
         <v>2022</v>
       </c>
@@ -20780,7 +20779,7 @@
         <v>233.22000000000003</v>
       </c>
     </row>
-    <row r="554" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A554" s="1">
         <v>2022</v>
       </c>
@@ -20819,7 +20818,7 @@
         <v>574.65</v>
       </c>
     </row>
-    <row r="555" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A555" s="1">
         <v>2022</v>
       </c>
@@ -20855,7 +20854,7 @@
         <v>899.1</v>
       </c>
     </row>
-    <row r="556" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A556" s="1">
         <v>2022</v>
       </c>
@@ -20894,7 +20893,7 @@
         <v>940.50000000000011</v>
       </c>
     </row>
-    <row r="557" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A557" s="1">
         <v>2022</v>
       </c>
@@ -20930,7 +20929,7 @@
         <v>287.52</v>
       </c>
     </row>
-    <row r="558" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A558" s="1">
         <v>2022</v>
       </c>
@@ -20966,7 +20965,7 @@
         <v>1208.1600000000001</v>
       </c>
     </row>
-    <row r="559" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A559" s="1">
         <v>2022</v>
       </c>
@@ -21002,7 +21001,7 @@
         <v>872.16000000000008</v>
       </c>
     </row>
-    <row r="560" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A560" s="1">
         <v>2022</v>
       </c>
@@ -21038,7 +21037,7 @@
         <v>1243.1999999999998</v>
       </c>
     </row>
-    <row r="561" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A561" s="1">
         <v>2022</v>
       </c>
@@ -21074,7 +21073,7 @@
         <v>1297.44</v>
       </c>
     </row>
-    <row r="562" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A562" s="1">
         <v>2022</v>
       </c>
@@ -21152,7 +21151,7 @@
         <v>4405.7</v>
       </c>
     </row>
-    <row r="564" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A564" s="1">
         <v>2022</v>
       </c>
@@ -21191,7 +21190,7 @@
         <v>2038.7499999999998</v>
       </c>
     </row>
-    <row r="565" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A565" s="1">
         <v>2022</v>
       </c>
@@ -21230,7 +21229,7 @@
         <v>1532.5</v>
       </c>
     </row>
-    <row r="566" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A566" s="1">
         <v>2022</v>
       </c>
@@ -21269,7 +21268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A567" s="1">
         <v>2022</v>
       </c>
@@ -21305,7 +21304,7 @@
         <v>943.6</v>
       </c>
     </row>
-    <row r="568" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A568" s="1">
         <v>2022</v>
       </c>
@@ -21341,7 +21340,7 @@
         <v>1522.5</v>
       </c>
     </row>
-    <row r="569" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A569" s="1">
         <v>2022</v>
       </c>
@@ -21377,7 +21376,7 @@
         <v>1008.7</v>
       </c>
     </row>
-    <row r="570" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A570" s="1">
         <v>2022</v>
       </c>
@@ -21413,7 +21412,7 @@
         <v>1511.3</v>
       </c>
     </row>
-    <row r="571" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A571" s="1">
         <v>2022</v>
       </c>
@@ -21449,7 +21448,7 @@
         <v>2203.65</v>
       </c>
     </row>
-    <row r="572" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A572" s="1">
         <v>2022</v>
       </c>
@@ -21485,7 +21484,7 @@
         <v>85.5</v>
       </c>
     </row>
-    <row r="573" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A573" s="1">
         <v>2022</v>
       </c>
@@ -21521,7 +21520,7 @@
         <v>867.35</v>
       </c>
     </row>
-    <row r="574" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A574" s="1">
         <v>2022</v>
       </c>
@@ -21560,7 +21559,7 @@
         <v>925.92</v>
       </c>
     </row>
-    <row r="575" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A575" s="1">
         <v>2022</v>
       </c>
@@ -21599,7 +21598,7 @@
         <v>411.36</v>
       </c>
     </row>
-    <row r="576" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A576" s="1">
         <v>2022</v>
       </c>
@@ -21638,7 +21637,7 @@
         <v>480.96</v>
       </c>
     </row>
-    <row r="577" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A577" s="1">
         <v>2022</v>
       </c>
@@ -21677,7 +21676,7 @@
         <v>670.08</v>
       </c>
     </row>
-    <row r="578" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A578" s="1">
         <v>2022</v>
       </c>
@@ -21716,7 +21715,7 @@
         <v>358.56</v>
       </c>
     </row>
-    <row r="579" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A579" s="1">
         <v>2022</v>
       </c>
@@ -21755,7 +21754,7 @@
         <v>1122.75</v>
       </c>
     </row>
-    <row r="580" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A580" s="1">
         <v>2022</v>
       </c>
@@ -21794,7 +21793,7 @@
         <v>371.25</v>
       </c>
     </row>
-    <row r="581" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A581" s="1">
         <v>2022</v>
       </c>
@@ -21833,7 +21832,7 @@
         <v>399.15</v>
       </c>
     </row>
-    <row r="582" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A582" s="1">
         <v>2022</v>
       </c>
@@ -21872,7 +21871,7 @@
         <v>141.96</v>
       </c>
     </row>
-    <row r="583" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A583" s="1">
         <v>2022</v>
       </c>
@@ -21911,7 +21910,7 @@
         <v>120.39999999999999</v>
       </c>
     </row>
-    <row r="584" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A584" s="1">
         <v>2022</v>
       </c>
@@ -21950,7 +21949,7 @@
         <v>931.05000000000007</v>
       </c>
     </row>
-    <row r="585" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A585" s="1">
         <v>2022</v>
       </c>
@@ -21986,7 +21985,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="586" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A586" s="1">
         <v>2022</v>
       </c>
@@ -22022,7 +22021,7 @@
         <v>2284.9900000000002</v>
       </c>
     </row>
-    <row r="587" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A587" s="1">
         <v>2022</v>
       </c>
@@ -22058,7 +22057,7 @@
         <v>3064.36</v>
       </c>
     </row>
-    <row r="588" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A588" s="1">
         <v>2022</v>
       </c>
@@ -22094,7 +22093,7 @@
         <v>3062.7</v>
       </c>
     </row>
-    <row r="589" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A589" s="1">
         <v>2022</v>
       </c>
@@ -22130,7 +22129,7 @@
         <v>957.83999999999992</v>
       </c>
     </row>
-    <row r="590" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A590" s="1">
         <v>2022</v>
       </c>
@@ -22166,7 +22165,7 @@
         <v>597.96</v>
       </c>
     </row>
-    <row r="591" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A591" s="1">
         <v>2022</v>
       </c>
@@ -22202,7 +22201,7 @@
         <v>1164.54</v>
       </c>
     </row>
-    <row r="592" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A592" s="1">
         <v>2022</v>
       </c>
@@ -22238,7 +22237,7 @@
         <v>2426.58</v>
       </c>
     </row>
-    <row r="593" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A593" s="1">
         <v>2022</v>
       </c>
@@ -22274,7 +22273,7 @@
         <v>1477.3200000000002</v>
       </c>
     </row>
-    <row r="594" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A594" s="1">
         <v>2022</v>
       </c>
@@ -22310,7 +22309,7 @@
         <v>1938.3000000000002</v>
       </c>
     </row>
-    <row r="595" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A595" s="1">
         <v>2022</v>
       </c>
@@ -22346,7 +22345,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="596" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A596" s="1">
         <v>2022</v>
       </c>
@@ -22382,7 +22381,7 @@
         <v>939.11999999999989</v>
       </c>
     </row>
-    <row r="597" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A597" s="1">
         <v>2022</v>
       </c>
@@ -22418,7 +22417,7 @@
         <v>1506.96</v>
       </c>
     </row>
-    <row r="598" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A598" s="1">
         <v>2022</v>
       </c>
@@ -22457,7 +22456,7 @@
         <v>3261.45</v>
       </c>
     </row>
-    <row r="599" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A599" s="1">
         <v>2022</v>
       </c>
@@ -22493,7 +22492,7 @@
         <v>1003.9799999999999</v>
       </c>
     </row>
-    <row r="600" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A600" s="1">
         <v>2022</v>
       </c>
@@ -22532,7 +22531,7 @@
         <v>1253.6400000000001</v>
       </c>
     </row>
-    <row r="601" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A601" s="1">
         <v>2022</v>
       </c>
@@ -22568,7 +22567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="602" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A602" s="1">
         <v>2023</v>
       </c>
@@ -22607,7 +22606,7 @@
         <v>1680.64</v>
       </c>
     </row>
-    <row r="603" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A603" s="1">
         <v>2023</v>
       </c>
@@ -22646,7 +22645,7 @@
         <v>2046.08</v>
       </c>
     </row>
-    <row r="604" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A604" s="1">
         <v>2023</v>
       </c>
@@ -22682,7 +22681,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="605" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A605" s="1">
         <v>2023</v>
       </c>
@@ -22718,7 +22717,7 @@
         <v>4976.16</v>
       </c>
     </row>
-    <row r="606" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A606" s="1">
         <v>2023</v>
       </c>
@@ -22754,7 +22753,7 @@
         <v>957.87</v>
       </c>
     </row>
-    <row r="607" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A607" s="1">
         <v>2023</v>
       </c>
@@ -22790,7 +22789,7 @@
         <v>658.80000000000007</v>
       </c>
     </row>
-    <row r="608" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A608" s="1">
         <v>2023</v>
       </c>
@@ -22826,7 +22825,7 @@
         <v>390.59999999999997</v>
       </c>
     </row>
-    <row r="609" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A609" s="1">
         <v>2023</v>
       </c>
@@ -22862,7 +22861,7 @@
         <v>680.4</v>
       </c>
     </row>
-    <row r="610" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A610" s="1">
         <v>2023</v>
       </c>
@@ -22898,7 +22897,7 @@
         <v>526.69999999999993</v>
       </c>
     </row>
-    <row r="611" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A611" s="1">
         <v>2023</v>
       </c>
@@ -22934,7 +22933,7 @@
         <v>937.8</v>
       </c>
     </row>
-    <row r="612" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A612" s="1">
         <v>2023</v>
       </c>
@@ -22970,7 +22969,7 @@
         <v>865.8</v>
       </c>
     </row>
-    <row r="613" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A613" s="1">
         <v>2023</v>
       </c>
@@ -23009,7 +23008,7 @@
         <v>402.04</v>
       </c>
     </row>
-    <row r="614" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A614" s="1">
         <v>2023</v>
       </c>
@@ -23048,7 +23047,7 @@
         <v>854.75</v>
       </c>
     </row>
-    <row r="615" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A615" s="1">
         <v>2023</v>
       </c>
@@ -23090,7 +23089,7 @@
         <v>466.44000000000005</v>
       </c>
     </row>
-    <row r="616" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A616" s="1">
         <v>2023</v>
       </c>
@@ -23126,7 +23125,7 @@
         <v>1149.3</v>
       </c>
     </row>
-    <row r="617" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A617" s="1">
         <v>2023</v>
       </c>
@@ -23165,7 +23164,7 @@
         <v>1698.3</v>
       </c>
     </row>
-    <row r="618" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A618" s="1">
         <v>2023</v>
       </c>
@@ -23201,7 +23200,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="619" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A619" s="1">
         <v>2023</v>
       </c>
@@ -23240,7 +23239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="620" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A620" s="1">
         <v>2023</v>
       </c>
@@ -23280,7 +23279,7 @@
       </c>
       <c r="N620" s="7"/>
     </row>
-    <row r="621" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A621" s="1">
         <v>2023</v>
       </c>
@@ -23316,7 +23315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="622" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A622" s="1">
         <v>2023</v>
       </c>
@@ -23355,7 +23354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="623" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A623" s="1">
         <v>2023</v>
       </c>
@@ -23394,7 +23393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="624" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A624" s="1">
         <v>2023</v>
       </c>
@@ -23466,7 +23465,7 @@
         <v>3795.6800000000003</v>
       </c>
     </row>
-    <row r="626" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A626" s="1">
         <v>2023</v>
       </c>
@@ -23502,7 +23501,7 @@
         <v>1353.7299999999998</v>
       </c>
     </row>
-    <row r="627" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A627" s="1">
         <v>2023</v>
       </c>
@@ -23538,7 +23537,7 @@
         <v>1152.44</v>
       </c>
     </row>
-    <row r="628" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A628" s="1">
         <v>2023</v>
       </c>
@@ -23574,7 +23573,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="629" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A629" s="1">
         <v>2023</v>
       </c>
@@ -23610,7 +23609,7 @@
         <v>876.2</v>
       </c>
     </row>
-    <row r="630" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A630" s="1">
         <v>2023</v>
       </c>
@@ -23646,7 +23645,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="631" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A631" s="1">
         <v>2023</v>
       </c>
@@ -23682,7 +23681,7 @@
         <v>749.32</v>
       </c>
     </row>
-    <row r="632" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A632" s="1">
         <v>2023</v>
       </c>
@@ -23718,7 +23717,7 @@
         <v>1122.68</v>
       </c>
     </row>
-    <row r="633" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A633" s="1">
         <v>2023</v>
       </c>
@@ -23757,7 +23756,7 @@
         <v>4505.24</v>
       </c>
     </row>
-    <row r="634" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A634" s="1">
         <v>2023</v>
       </c>
@@ -23793,7 +23792,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="635" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A635" s="1">
         <v>2023</v>
       </c>
@@ -23829,7 +23828,7 @@
         <v>684.75000000000011</v>
       </c>
     </row>
-    <row r="636" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A636" s="1">
         <v>2023</v>
       </c>
@@ -23865,7 +23864,7 @@
         <v>2160.48</v>
       </c>
     </row>
-    <row r="637" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A637" s="1">
         <v>2023</v>
       </c>
@@ -23901,7 +23900,7 @@
         <v>959.84</v>
       </c>
     </row>
-    <row r="638" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A638" s="1">
         <v>2023</v>
       </c>
@@ -23937,7 +23936,7 @@
         <v>1122.24</v>
       </c>
     </row>
-    <row r="639" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A639" s="1">
         <v>2023</v>
       </c>
@@ -23973,7 +23972,7 @@
         <v>1563.52</v>
       </c>
     </row>
-    <row r="640" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A640" s="1">
         <v>2023</v>
       </c>
@@ -24009,7 +24008,7 @@
         <v>836.64</v>
       </c>
     </row>
-    <row r="641" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A641" s="1">
         <v>2023</v>
       </c>
@@ -24045,7 +24044,7 @@
         <v>2245.5</v>
       </c>
     </row>
-    <row r="642" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A642" s="1">
         <v>2023</v>
       </c>
@@ -24081,7 +24080,7 @@
         <v>684.75</v>
       </c>
     </row>
-    <row r="643" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A643" s="1">
         <v>2023</v>
       </c>
@@ -24117,7 +24116,7 @@
         <v>736.20999999999992</v>
       </c>
     </row>
-    <row r="644" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A644" s="1">
         <v>2023</v>
       </c>
@@ -24153,7 +24152,7 @@
         <v>207.48000000000002</v>
       </c>
     </row>
-    <row r="645" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A645" s="1">
         <v>2023</v>
       </c>
@@ -24189,7 +24188,7 @@
         <v>174.57999999999998</v>
       </c>
     </row>
-    <row r="646" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A646" s="1">
         <v>2023</v>
       </c>
@@ -24225,7 +24224,7 @@
         <v>1862.1000000000001</v>
       </c>
     </row>
-    <row r="647" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A647" s="1">
         <v>2023</v>
       </c>
@@ -24261,7 +24260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="648" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A648" s="1">
         <v>2023</v>
       </c>
@@ -24297,7 +24296,7 @@
         <v>2174.87</v>
       </c>
     </row>
-    <row r="649" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A649" s="1">
         <v>2023</v>
       </c>
@@ -24333,7 +24332,7 @@
         <v>2916.6800000000003</v>
       </c>
     </row>
-    <row r="650" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A650" s="1">
         <v>2023</v>
       </c>
@@ -24369,7 +24368,7 @@
         <v>2915.1</v>
       </c>
     </row>
-    <row r="651" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A651" s="1">
         <v>2023</v>
       </c>
@@ -24405,7 +24404,7 @@
         <v>970.12</v>
       </c>
     </row>
-    <row r="652" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A652" s="1">
         <v>2023</v>
       </c>
@@ -24441,7 +24440,7 @@
         <v>362.4</v>
       </c>
     </row>
-    <row r="653" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A653" s="1">
         <v>2023</v>
       </c>
@@ -24477,7 +24476,7 @@
         <v>1269.05</v>
       </c>
     </row>
-    <row r="654" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A654" s="1">
         <v>2023</v>
       </c>
@@ -24513,7 +24512,7 @@
         <v>2457.69</v>
       </c>
     </row>
-    <row r="655" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A655" s="1">
         <v>2023</v>
       </c>
@@ -24549,7 +24548,7 @@
         <v>1496.26</v>
       </c>
     </row>
-    <row r="656" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A656" s="1">
         <v>2023</v>
       </c>
@@ -24585,7 +24584,7 @@
         <v>1963.15</v>
       </c>
     </row>
-    <row r="657" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A657" s="1">
         <v>2023</v>
       </c>
@@ -24621,7 +24620,7 @@
         <v>2093.5</v>
       </c>
     </row>
-    <row r="658" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A658" s="1">
         <v>2023</v>
       </c>
@@ -24657,7 +24656,7 @@
         <v>951.16</v>
       </c>
     </row>
-    <row r="659" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A659" s="1">
         <v>2023</v>
       </c>
@@ -24693,7 +24692,7 @@
         <v>1526.28</v>
       </c>
     </row>
-    <row r="660" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A660" s="1">
         <v>2023</v>
       </c>
@@ -24729,7 +24728,7 @@
         <v>4220.7</v>
       </c>
     </row>
-    <row r="661" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A661" s="1">
         <v>2023</v>
       </c>
@@ -24765,7 +24764,7 @@
         <v>1003.9799999999999</v>
       </c>
     </row>
-    <row r="662" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A662" s="1">
         <v>2023</v>
       </c>
@@ -24801,7 +24800,7 @@
         <v>1186.24</v>
       </c>
     </row>
-    <row r="663" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A663" s="1">
         <v>2023</v>
       </c>
@@ -24840,7 +24839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="664" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A664" s="1">
         <v>2024</v>
       </c>
@@ -24875,7 +24874,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="665" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A665" s="1">
         <v>2024</v>
       </c>
@@ -24910,7 +24909,7 @@
         <v>2495.69</v>
       </c>
     </row>
-    <row r="666" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A666" s="1">
         <v>2024</v>
       </c>
@@ -24945,7 +24944,7 @@
         <v>1663.8620000000001</v>
       </c>
     </row>
-    <row r="667" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A667" s="1">
         <v>2024</v>
       </c>
@@ -24980,7 +24979,7 @@
         <v>4665.1499999999996</v>
       </c>
     </row>
-    <row r="668" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A668" s="1">
         <v>2024</v>
       </c>
@@ -25015,7 +25014,7 @@
         <v>825.75</v>
       </c>
     </row>
-    <row r="669" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A669" s="1">
         <v>2024</v>
       </c>
@@ -25050,7 +25049,7 @@
         <v>658.80000000000007</v>
       </c>
     </row>
-    <row r="670" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A670" s="1">
         <v>2024</v>
       </c>
@@ -25085,7 +25084,7 @@
         <v>390.59999999999997</v>
       </c>
     </row>
-    <row r="671" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A671" s="1">
         <v>2024</v>
       </c>
@@ -25120,7 +25119,7 @@
         <v>680.4</v>
       </c>
     </row>
-    <row r="672" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A672" s="1">
         <v>2024</v>
       </c>
@@ -25158,7 +25157,7 @@
         <v>858.75</v>
       </c>
     </row>
-    <row r="673" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A673" s="1">
         <v>2024</v>
       </c>
@@ -25193,7 +25192,7 @@
         <v>937.8</v>
       </c>
     </row>
-    <row r="674" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A674" s="1">
         <v>2024</v>
       </c>
@@ -25228,7 +25227,7 @@
         <v>865.8</v>
       </c>
     </row>
-    <row r="675" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A675" s="1">
         <v>2024</v>
       </c>
@@ -25263,7 +25262,7 @@
         <v>416.09999999999997</v>
       </c>
     </row>
-    <row r="676" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A676" s="1">
         <v>2024</v>
       </c>
@@ -25298,7 +25297,7 @@
         <v>1262.55</v>
       </c>
     </row>
-    <row r="677" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A677" s="1">
         <v>2024</v>
       </c>
@@ -25339,7 +25338,7 @@
         <v>456.3</v>
       </c>
     </row>
-    <row r="678" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A678" s="1">
         <v>2024</v>
       </c>
@@ -25374,7 +25373,7 @@
         <v>1149.3</v>
       </c>
     </row>
-    <row r="679" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A679" s="1">
         <v>2024</v>
       </c>
@@ -25409,7 +25408,7 @@
         <v>2078.54</v>
       </c>
     </row>
-    <row r="680" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A680" s="1">
         <v>2024</v>
       </c>
@@ -25444,7 +25443,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="681" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A681" s="1">
         <v>2024</v>
       </c>
@@ -25482,7 +25481,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="682" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A682" s="1">
         <v>2024</v>
       </c>
@@ -25520,7 +25519,7 @@
         <v>1645.92</v>
       </c>
     </row>
-    <row r="683" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A683" s="1">
         <v>2024</v>
       </c>
@@ -25558,7 +25557,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="684" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A684" s="1">
         <v>2024</v>
       </c>
@@ -25596,7 +25595,7 @@
         <v>3496.5</v>
       </c>
     </row>
-    <row r="685" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A685" s="1">
         <v>2024</v>
       </c>
@@ -25634,7 +25633,7 @@
         <v>3514.9811999999997</v>
       </c>
     </row>
-    <row r="686" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A686" s="1">
         <v>2024</v>
       </c>
@@ -25704,7 +25703,7 @@
         <v>3456.78</v>
       </c>
     </row>
-    <row r="688" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A688" s="1">
         <v>2024</v>
       </c>
@@ -25739,7 +25738,7 @@
         <v>1663.62</v>
       </c>
     </row>
-    <row r="689" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A689" s="1">
         <v>2024</v>
       </c>
@@ -25774,7 +25773,7 @@
         <v>1250.52</v>
       </c>
     </row>
-    <row r="690" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A690" s="1">
         <v>2024</v>
       </c>
@@ -25809,7 +25808,7 @@
         <v>1055.42</v>
       </c>
     </row>
-    <row r="691" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A691" s="1">
         <v>2024</v>
       </c>
@@ -25844,7 +25843,7 @@
         <v>795.32</v>
       </c>
     </row>
-    <row r="692" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A692" s="1">
         <v>2024</v>
       </c>
@@ -25882,7 +25881,7 @@
         <v>1848.75</v>
       </c>
     </row>
-    <row r="693" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A693" s="1">
         <v>2024</v>
       </c>
@@ -25920,7 +25919,7 @@
         <v>1080.75</v>
       </c>
     </row>
-    <row r="694" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A694" s="1">
         <v>2024</v>
       </c>
@@ -25958,7 +25957,7 @@
         <v>1619.25</v>
       </c>
     </row>
-    <row r="695" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A695" s="1">
         <v>2024</v>
       </c>
@@ -25993,7 +25992,7 @@
         <v>5826.54</v>
       </c>
     </row>
-    <row r="696" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A696" s="1">
         <v>2024</v>
       </c>
@@ -26028,7 +26027,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="697" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A697" s="1">
         <v>2024</v>
       </c>
@@ -26063,7 +26062,7 @@
         <v>730.40000000000009</v>
       </c>
     </row>
-    <row r="698" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A698" s="1">
         <v>2024</v>
       </c>
@@ -26098,7 +26097,7 @@
         <v>2064.0299999999997</v>
       </c>
     </row>
-    <row r="699" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A699" s="1">
         <v>2024</v>
       </c>
@@ -26133,7 +26132,7 @@
         <v>916.99</v>
       </c>
     </row>
-    <row r="700" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A700" s="1">
         <v>2024</v>
       </c>
@@ -26168,7 +26167,7 @@
         <v>1072.1399999999999</v>
       </c>
     </row>
-    <row r="701" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A701" s="1">
         <v>2024</v>
       </c>
@@ -26203,7 +26202,7 @@
         <v>1493.72</v>
       </c>
     </row>
-    <row r="702" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A702" s="1">
         <v>2024</v>
       </c>
@@ -26238,7 +26237,7 @@
         <v>799.29</v>
       </c>
     </row>
-    <row r="703" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A703" s="1">
         <v>2024</v>
       </c>
@@ -26273,7 +26272,7 @@
         <v>2245.5</v>
       </c>
     </row>
-    <row r="704" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A704" s="1">
         <v>2024</v>
       </c>
@@ -26308,7 +26307,7 @@
         <v>841.5</v>
       </c>
     </row>
-    <row r="705" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A705" s="1">
         <v>2024</v>
       </c>
@@ -26343,7 +26342,7 @@
         <v>904.7399999999999</v>
       </c>
     </row>
-    <row r="706" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A706" s="1">
         <v>2024</v>
       </c>
@@ -26378,7 +26377,7 @@
         <v>305.76</v>
       </c>
     </row>
-    <row r="707" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A707" s="1">
         <v>2024</v>
       </c>
@@ -26413,7 +26412,7 @@
         <v>252.83999999999997</v>
       </c>
     </row>
-    <row r="708" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A708" s="1">
         <v>2024</v>
       </c>
@@ -26448,7 +26447,7 @@
         <v>1862.1000000000001</v>
       </c>
     </row>
-    <row r="709" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A709" s="1">
         <v>2024</v>
       </c>
@@ -26486,7 +26485,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="710" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A710" s="1">
         <v>2024</v>
       </c>
@@ -26521,7 +26520,7 @@
         <v>2477.7000000000003</v>
       </c>
     </row>
-    <row r="711" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A711" s="1">
         <v>2024</v>
       </c>
@@ -26556,7 +26555,7 @@
         <v>3322.8</v>
       </c>
     </row>
-    <row r="712" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A712" s="1">
         <v>2024</v>
       </c>
@@ -26591,7 +26590,7 @@
         <v>3321</v>
       </c>
     </row>
-    <row r="713" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A713" s="1">
         <v>2024</v>
       </c>
@@ -26626,7 +26625,7 @@
         <v>835.04</v>
       </c>
     </row>
-    <row r="714" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A714" s="1">
         <v>2024</v>
       </c>
@@ -26664,7 +26663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="715" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A715" s="1">
         <v>2024</v>
       </c>
@@ -26699,7 +26698,7 @@
         <v>1074.96</v>
       </c>
     </row>
-    <row r="716" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A716" s="1">
         <v>2024</v>
       </c>
@@ -26734,7 +26733,7 @@
         <v>1679.94</v>
       </c>
     </row>
-    <row r="717" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A717" s="1">
         <v>2024</v>
       </c>
@@ -26769,7 +26768,7 @@
         <v>1496.26</v>
       </c>
     </row>
-    <row r="718" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A718" s="1">
         <v>2024</v>
       </c>
@@ -26804,7 +26803,7 @@
         <v>1341.9</v>
       </c>
     </row>
-    <row r="719" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A719" s="1">
         <v>2024</v>
       </c>
@@ -26839,7 +26838,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="720" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A720" s="1">
         <v>2024</v>
       </c>
@@ -26874,7 +26873,7 @@
         <v>818.71999999999991</v>
       </c>
     </row>
-    <row r="721" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A721" s="1">
         <v>2024</v>
       </c>
@@ -26909,7 +26908,7 @@
         <v>1313.76</v>
       </c>
     </row>
-    <row r="722" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A722" s="1">
         <v>2024</v>
       </c>
@@ -26944,7 +26943,7 @@
         <v>3606.7799999999997</v>
       </c>
     </row>
-    <row r="723" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A723" s="1">
         <v>2024</v>
       </c>
@@ -26979,7 +26978,7 @@
         <v>865.49999999999989</v>
       </c>
     </row>
-    <row r="724" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A724" s="1">
         <v>2024</v>
       </c>
@@ -27014,7 +27013,7 @@
         <v>1827.8879999999999</v>
       </c>
     </row>
-    <row r="725" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A725" s="1">
         <v>2024</v>
       </c>
@@ -27052,7 +27051,7 @@
         <v>5625</v>
       </c>
     </row>
-    <row r="726" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A726" s="1">
         <v>2025</v>
       </c>
@@ -27088,7 +27087,7 @@
         <v>436.21</v>
       </c>
     </row>
-    <row r="727" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A727" s="1">
         <v>2026</v>
       </c>
@@ -27125,7 +27124,7 @@
         <v>1226.1053999999999</v>
       </c>
     </row>
-    <row r="728" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A728" s="1">
         <v>2026</v>
       </c>
@@ -27162,7 +27161,7 @@
         <v>1635.8003999999999</v>
       </c>
     </row>
-    <row r="729" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A729" s="1">
         <v>2026</v>
       </c>
@@ -27199,7 +27198,7 @@
         <v>1624.2486000000001</v>
       </c>
     </row>
-    <row r="730" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A730" s="1">
         <v>2026</v>
       </c>
@@ -27236,7 +27235,7 @@
         <v>3393.3886000000002</v>
       </c>
     </row>
-    <row r="731" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A731" s="1">
         <v>2026</v>
       </c>
@@ -27275,7 +27274,7 @@
         <v>773.87310000000002</v>
       </c>
     </row>
-    <row r="732" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A732" s="1">
         <v>2026</v>
       </c>
@@ -27312,7 +27311,7 @@
         <v>504.49560000000002</v>
       </c>
     </row>
-    <row r="733" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A733" s="1">
         <v>2026</v>
       </c>
@@ -27349,7 +27348,7 @@
         <v>378.75740000000002</v>
       </c>
     </row>
-    <row r="734" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A734" s="1">
         <v>2026</v>
       </c>
@@ -27386,7 +27385,7 @@
         <v>556.95079999999996</v>
       </c>
     </row>
-    <row r="735" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A735" s="1">
         <v>2026</v>
       </c>
@@ -27423,7 +27422,7 @@
         <v>1108.6753999999999</v>
       </c>
     </row>
-    <row r="736" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A736" s="1">
         <v>2026</v>
       </c>
@@ -27460,7 +27459,7 @@
         <v>790.68500000000006</v>
       </c>
     </row>
-    <row r="737" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A737" s="1">
         <v>2026</v>
       </c>
@@ -27497,7 +27496,7 @@
         <v>742.85820000000001</v>
       </c>
     </row>
-    <row r="738" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A738" s="1">
         <v>2026</v>
       </c>
@@ -27534,7 +27533,7 @@
         <v>316.58249999999998</v>
       </c>
     </row>
-    <row r="739" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A739" s="1">
         <v>2026</v>
       </c>
@@ -27571,7 +27570,7 @@
         <v>968.36999999999989</v>
       </c>
     </row>
-    <row r="740" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A740" s="1">
         <v>2026</v>
       </c>
@@ -27613,7 +27612,7 @@
         <v>391.87119999999999</v>
       </c>
     </row>
-    <row r="741" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A741" s="1">
         <v>2026</v>
       </c>
@@ -27650,7 +27649,7 @@
         <v>996.64880000000005</v>
       </c>
     </row>
-    <row r="742" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A742" s="1">
         <v>2026</v>
       </c>
@@ -27687,7 +27686,7 @@
         <v>1471.9223999999999</v>
       </c>
     </row>
-    <row r="743" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A743" s="1">
         <v>2026</v>
       </c>
@@ -27724,7 +27723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="744" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A744" s="1">
         <v>2026</v>
       </c>
@@ -27761,7 +27760,7 @@
         <v>902.8187999999999</v>
       </c>
     </row>
-    <row r="745" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A745" s="1">
         <v>2026</v>
       </c>
@@ -27798,7 +27797,7 @@
         <v>851.4206999999999</v>
       </c>
     </row>
-    <row r="746" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A746" s="1">
         <v>2026</v>
       </c>
@@ -27835,7 +27834,7 @@
         <v>1415.31</v>
       </c>
     </row>
-    <row r="747" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A747" s="1">
         <v>2026</v>
       </c>
@@ -27872,7 +27871,7 @@
         <v>2085.7199999999998</v>
       </c>
     </row>
-    <row r="748" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A748" s="1">
         <v>2026</v>
       </c>
@@ -27909,7 +27908,7 @@
         <v>2485.7312999999995</v>
       </c>
     </row>
-    <row r="749" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A749" s="1">
         <v>2026</v>
       </c>
@@ -27985,7 +27984,7 @@
         <v>2640.5021999999999</v>
       </c>
     </row>
-    <row r="751" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A751" s="1">
         <v>2026</v>
       </c>
@@ -28024,7 +28023,7 @@
         <v>1291.8501000000001</v>
       </c>
     </row>
-    <row r="752" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A752" s="1">
         <v>2026</v>
       </c>
@@ -28063,7 +28062,7 @@
         <v>930.81239999999991</v>
       </c>
     </row>
-    <row r="753" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A753" s="1">
         <v>2026</v>
       </c>
@@ -28100,7 +28099,7 @@
         <v>656.25689999999997</v>
       </c>
     </row>
-    <row r="754" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A754" s="1">
         <v>2026</v>
       </c>
@@ -28137,7 +28136,7 @@
         <v>1380.7190000000001</v>
       </c>
     </row>
-    <row r="755" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A755" s="1">
         <v>2026</v>
       </c>
@@ -28174,7 +28173,7 @@
         <v>1955.6047000000001</v>
       </c>
     </row>
-    <row r="756" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A756" s="1">
         <v>2026</v>
       </c>
@@ -28211,7 +28210,7 @@
         <v>1494.175</v>
       </c>
     </row>
-    <row r="757" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A757" s="1">
         <v>2026</v>
       </c>
@@ -28248,7 +28247,7 @@
         <v>2222.5219999999999</v>
       </c>
     </row>
-    <row r="758" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A758" s="1">
         <v>2026</v>
       </c>
@@ -28285,7 +28284,7 @@
         <v>3807.1838999999995</v>
       </c>
     </row>
-    <row r="759" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A759" s="1">
         <v>2026</v>
       </c>
@@ -28324,7 +28323,7 @@
         <v>85.041000000000011</v>
       </c>
     </row>
-    <row r="760" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A760" s="1">
         <v>2026</v>
       </c>
@@ -28363,7 +28362,7 @@
         <v>719.75610000000006</v>
       </c>
     </row>
-    <row r="761" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A761" s="1">
         <v>2026</v>
       </c>
@@ -28400,7 +28399,7 @@
         <v>1537.4002</v>
       </c>
     </row>
-    <row r="762" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A762" s="1">
         <v>2026</v>
       </c>
@@ -28437,7 +28436,7 @@
         <v>658.00419999999997</v>
       </c>
     </row>
-    <row r="763" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A763" s="1">
         <v>2026</v>
       </c>
@@ -28474,7 +28473,7 @@
         <v>698.11700000000008</v>
       </c>
     </row>
-    <row r="764" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A764" s="1">
         <v>2026</v>
       </c>
@@ -28511,7 +28510,7 @@
         <v>1064.5320000000002</v>
       </c>
     </row>
-    <row r="765" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A765" s="1">
         <v>2026</v>
       </c>
@@ -28548,7 +28547,7 @@
         <v>560.03639999999996</v>
       </c>
     </row>
-    <row r="766" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A766" s="1">
         <v>2026</v>
       </c>
@@ -28585,7 +28584,7 @@
         <v>1909.9864000000002</v>
       </c>
     </row>
-    <row r="767" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A767" s="1">
         <v>2026</v>
       </c>
@@ -28622,7 +28621,7 @@
         <v>24.684799999999999</v>
       </c>
     </row>
-    <row r="768" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A768" s="1">
         <v>2026</v>
       </c>
@@ -28659,7 +28658,7 @@
         <v>1275.8955999999998</v>
       </c>
     </row>
-    <row r="769" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A769" s="1">
         <v>2026</v>
       </c>
@@ -28698,7 +28697,7 @@
         <v>283.72770000000003</v>
       </c>
     </row>
-    <row r="770" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A770" s="1">
         <v>2026</v>
       </c>
@@ -28737,7 +28736,7 @@
         <v>231.15690000000004</v>
       </c>
     </row>
-    <row r="771" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A771" s="1">
         <v>2026</v>
       </c>
@@ -28774,7 +28773,7 @@
         <v>1601.4264000000001</v>
       </c>
     </row>
-    <row r="772" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A772" s="1">
         <v>2026</v>
       </c>
@@ -28811,7 +28810,7 @@
         <v>4018.5709999999999</v>
       </c>
     </row>
-    <row r="773" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A773" s="1">
         <v>2026</v>
       </c>
@@ -28850,7 +28849,7 @@
         <v>2086.5969</v>
       </c>
     </row>
-    <row r="774" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A774" s="1">
         <v>2026</v>
       </c>
@@ -28887,7 +28886,7 @@
         <v>1696.6864</v>
       </c>
     </row>
-    <row r="775" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A775" s="1">
         <v>2026</v>
       </c>
@@ -28926,7 +28925,7 @@
         <v>2962.5192000000002</v>
       </c>
     </row>
-    <row r="776" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A776" s="1">
         <v>2026</v>
       </c>
@@ -28965,7 +28964,7 @@
         <v>1477.3127000000002</v>
       </c>
     </row>
-    <row r="777" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A777" s="1">
         <v>2026</v>
       </c>
@@ -29002,7 +29001,7 @@
         <v>570.2011</v>
       </c>
     </row>
-    <row r="778" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A778" s="1">
         <v>2026</v>
       </c>
@@ -29039,7 +29038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="779" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A779" s="1">
         <v>2026</v>
       </c>
@@ -29078,7 +29077,7 @@
         <v>3709.7234000000003</v>
       </c>
     </row>
-    <row r="780" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A780" s="1">
         <v>2026</v>
       </c>
@@ -29117,7 +29116,7 @@
         <v>1476.6210000000001</v>
       </c>
     </row>
-    <row r="781" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A781" s="1">
         <v>2026</v>
       </c>
@@ -29154,7 +29153,7 @@
         <v>2512.2399999999998</v>
       </c>
     </row>
-    <row r="782" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A782" s="1">
         <v>2026</v>
       </c>
@@ -29193,7 +29192,7 @@
         <v>2038.6647</v>
       </c>
     </row>
-    <row r="783" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A783" s="1">
         <v>2026</v>
       </c>
@@ -29230,7 +29229,7 @@
         <v>1275.367</v>
       </c>
     </row>
-    <row r="784" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A784" s="1">
         <v>2026</v>
       </c>
@@ -29269,7 +29268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="785" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A785" s="1">
         <v>2026</v>
       </c>
@@ -29306,7 +29305,7 @@
         <v>2935.1769999999997</v>
       </c>
     </row>
-    <row r="786" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A786" s="1">
         <v>2026</v>
       </c>
@@ -29345,7 +29344,7 @@
         <v>950.13990000000001</v>
       </c>
     </row>
-    <row r="787" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A787" s="1">
         <v>2026</v>
       </c>
@@ -29382,7 +29381,7 @@
         <v>1004.1251999999999</v>
       </c>
     </row>
-    <row r="788" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A788" s="1">
         <v>2026</v>
       </c>
@@ -29420,13 +29419,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L788" xr:uid="{05B88DED-2186-4B06-A0DC-FB0B7B55563E}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="30"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L788" xr:uid="{05B88DED-2186-4B06-A0DC-FB0B7B55563E}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -32740,6 +32733,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="6ef6f789-57f9-4e59-aa4a-cd15f71f422b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100BA5C067DE259F44BBE6385166EE14E35" ma:contentTypeVersion="12" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="e0b858a09c7922bcf5eecab13fb6d744">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="6ef6f789-57f9-4e59-aa4a-cd15f71f422b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8c891a16625b915cd9948935273f536c" ns3:_="">
     <xsd:import namespace="6ef6f789-57f9-4e59-aa4a-cd15f71f422b"/>
@@ -32933,37 +32943,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="6ef6f789-57f9-4e59-aa4a-cd15f71f422b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B7CBF56-A92F-43B0-98DD-230595657978}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6229DE72-183E-4476-9953-6132ACCD11EA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="6ef6f789-57f9-4e59-aa4a-cd15f71f422b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -32985,9 +32968,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6229DE72-183E-4476-9953-6132ACCD11EA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B7CBF56-A92F-43B0-98DD-230595657978}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6ef6f789-57f9-4e59-aa4a-cd15f71f422b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>